--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look</t>
   </si>
   <si>
-    <t xml:space="preserve">This list contains a week-by-week view of  MoJ Official and National Statistics that have been pre-announced on the gov.uk release calendar as at 14 November 2025</t>
+    <t xml:space="preserve">This list contains a week-by-week view of  MoJ Official and National Statistics that have been pre-announced on the gov.uk release calendar as at 20 November 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
@@ -41,13 +41,16 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">17 Nov 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knife and Offensive Weapon Sentencing Statistics:  April to June 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 November 2025</t>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Nov 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Her Majesty’s Prison and Probation Service Staff Equalities Report: 2024 to 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 November 2025</t>
   </si>
   <si>
     <t xml:space="preserve">confirmed</t>
@@ -56,36 +59,39 @@
     <t xml:space="preserve">standard</t>
   </si>
   <si>
-    <t xml:space="preserve"> HM Prison and Probation Service workforce quarterly: September 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 Nov 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Her Majesty’s Prison and Probation Service Staff Equalities Report: 2024 to 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 November 2025</t>
+    <t xml:space="preserve">The HMPPS annual Staff Equalities Report considers profiles and processes of the HMPPS workforce from an equalities perspective.</t>
   </si>
   <si>
     <t xml:space="preserve">His Majesty’s Prison and Probation Service offender equalities report: 2024 to 2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Equalities-focused tables and commentary encompassing a wide range of issues relating to offenders across prisons and probation.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ethnicity and the Criminal Justice System 2024</t>
   </si>
   <si>
+    <t xml:space="preserve">This report compiles statistics from data sources across the Criminal Justice System, to provide a combined perspective on the typical experiences of different ethnic groups in England and Wales.</t>
+  </si>
+  <si>
     <t xml:space="preserve">01 Dec 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> Civil justice statistics: July to September 2025</t>
+    <t xml:space="preserve">Civil justice statistics: July to September 2025</t>
   </si>
   <si>
     <t xml:space="preserve">4 December 2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Volume of civil and judicial review cases dealt with by the courts over time and the overall timeliness of these cases.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prison Population Projections: 2025 to 2030</t>
   </si>
   <si>
+    <t xml:space="preserve">Five year projections for the population in England and Wales prisons.</t>
+  </si>
+  <si>
     <t xml:space="preserve">08 Dec 2025</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
     <t xml:space="preserve">11 December 2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Type and volume of tribunal cases received, disposed of or outstanding. This also includes statistics on the Gender Recognition Certificate applied for and granted by HMCTS Gender Recognition Panel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">15 Dec 2025</t>
   </si>
   <si>
@@ -104,40 +113,64 @@
     <t xml:space="preserve">18 December 2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Volume of cases dealt with by family courts over time, with statistics also broken down for the main types of case involved. Includes data on Children Act cases (both public and private law), Matrimonial matters, Domestic Violence Remedy Orders, Forced Marriage Protection Orders, Female Genital Mutilation Protection Orders, adoptions, The Mental Capacity Act and probate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criminal court statistics quarterly: July to September 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type and volume of cases received and processed through the criminal court system of England and Wales, including statistics on case timeliness. Also includes statistics on the use of language interpreter and translation services in courts and tribunals, England and Wales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal aid statistics quarterly: July to September 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cancelled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity in the legal aid system for England and Wales, including criminal and civil legal aid, family mediation, providers of legal aid, client characteristics and Central Funds payments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 Dec 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 Jan 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Jan 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Jan 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Jan 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety in custody: quarterly update to September 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 January 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly update on deaths, self-harm and assaults in prison custody in England and Wales. Additional annual deaths tables (to 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 Feb 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 Feb 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage and landlord possession statistics: October to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 February 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">provisional</t>
   </si>
   <si>
-    <t xml:space="preserve">Criminal court statistics quarterly: July to September 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal aid statistics quarterly: July to September 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 Dec 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 Jan 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Jan 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 Jan 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 Jan 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safety in custody: quarterly update to September 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 January 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 Feb 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 Feb 2026</t>
+    <t xml:space="preserve">Quarterly National Statistics on possession claim actions in county courts by mortgage lenders and social and private landlords.</t>
   </si>
   <si>
     <t xml:space="preserve">16 Feb 2026</t>
@@ -230,12 +263,21 @@
     <t xml:space="preserve">30 July 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Annual release on employment status of offenders post release from custody and on community sentences. Covers employment rates, and those who are unable to work.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Offender accommodation outcomes, update to March 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Annual release on accommodation status of offenders post release from custody and on community sentences. Covers those who are housed, homeless or rough sleeping.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Community Performance Annual, update to March 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">An annual release of performance statistics for the Probation Service, incorporating Probation Service and Commissioned Rehabilitative Services performance.</t>
+  </si>
+  <si>
     <t xml:space="preserve">03 Aug 2026</t>
   </si>
   <si>
@@ -285,6 +327,9 @@
   </si>
   <si>
     <t xml:space="preserve">29 October 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of deaths of offenders supervised in the community by the Probation Service in England and Wales</t>
   </si>
 </sst>
 </file>
@@ -354,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -364,6 +409,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -718,10 +769,11 @@
   <cols>
     <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="95.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="30.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="10.71" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="60.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,845 +810,907 @@
       <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>51</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>30</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>30</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21" s="5"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F24" s="5"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25" s="5"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F26" s="5"/>
+        <v>13</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>30</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F36" s="5"/>
+      <c r="G36" s="6"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F37" s="5"/>
+      <c r="G37" s="6"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F38" s="5"/>
+      <c r="G38" s="6"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F39" s="5"/>
+      <c r="G39" s="6"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
+        <v>74</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="F40" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F41" s="5"/>
+      <c r="G41" s="6"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>30</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
       <c r="E42" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F42" s="5"/>
+      <c r="G42" s="6"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F43" s="5"/>
+      <c r="G43" s="6"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E44" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="F44" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E45" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F45" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>31</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
       <c r="E47" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="F47" s="5"/>
+      <c r="G47" s="6"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
       <c r="E48" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F48" s="5"/>
+      <c r="G48" s="6"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F49" s="5"/>
+      <c r="G49" s="6"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F50" s="5"/>
+      <c r="G50" s="6"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F51" s="5"/>
+      <c r="G51" s="6"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F52" s="5"/>
+      <c r="G52" s="6"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F53" s="5"/>
+      <c r="G53" s="6"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F54" s="5"/>
+      <c r="G54" s="6"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
+        <v>96</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E55" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="F55" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F56" s="5"/>
+      <c r="G56" s="6"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>30</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
       <c r="E57" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F57" s="5"/>
+      <c r="G57" s="6"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F58" s="5"/>
+      <c r="G58" s="6"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
+        <v>102</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E59" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="F59" s="5"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="F60" s="5"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>13</v>
+      <c r="F59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:F61">
+  <conditionalFormatting sqref="A5:G59">
     <cfRule type="expression" dxfId="0" priority="5">
       <formula>=AND(LEN($E5)&gt;0,MOD(RIGHT($E5,2),2)=0)</formula>
     </cfRule>
@@ -1607,7 +1721,7 @@
       <formula>=AND($E5&lt;&gt;$E4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A61">
+  <conditionalFormatting sqref="A5:A59">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>=AND(LEN($E5)&gt;0,MOD(RIGHT($E5,2),2)=0,$E5=$E4)</formula>
     </cfRule>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Weekly View)</t>
   </si>
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Last updated:  Thursday 26 February 2026</t>
+    <t xml:space="preserve">Last updated:  Thursday 05 March 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Week Commencing</t>
@@ -52,28 +52,25 @@
     <t xml:space="preserve">Usual publication month(s)</t>
   </si>
   <si>
-    <t xml:space="preserve">February 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 23 Feb 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">March 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Mon 02 Mar 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Civil justice statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 05 Mar 2026</t>
+    <t xml:space="preserve">Mon 09 Mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tribunals statistics quarterly: October to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 12 Mar 2026</t>
   </si>
   <si>
     <t xml:space="preserve">confirmed</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 05 Feb 2026</t>
+    <t xml:space="preserve">Thu 12 Feb 2026</t>
   </si>
   <si>
     <t xml:space="preserve">standard</t>
@@ -82,18 +79,6 @@
     <t xml:space="preserve">Mar, Jun, Sep, Dec </t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 09 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tribunals statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 12 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 12 Feb 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mon 16 Mar 2026</t>
   </si>
   <si>
@@ -688,9 +673,6 @@
     <t xml:space="preserve">Publication series</t>
   </si>
   <si>
-    <t xml:space="preserve">Feb 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mar 2026</t>
   </si>
   <si>
@@ -733,9 +715,6 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">Thu 05 Mar 2026 (confirmed)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thu 04 Jun 2026 (provisional)</t>
   </si>
   <si>
@@ -1018,70 +997,73 @@
     <t xml:space="preserve">Matteo Chiesa</t>
   </si>
   <si>
+    <t xml:space="preserve">Carly Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cajs@justice.gov.uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henry Goldsack/John Alexander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ed Rowland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Kelleher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">communityperformanceenquiries@justice.gov.uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJS@justice.gov.uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Rudling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criminal_court_sta@justice.gov.uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fazeen Khamkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CJS_Statistics@justice.gov.uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrea Solomou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liz Whiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probation-statistics-enquiries@justice.gov.uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wincen Lowe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rita Kumi-Ampofo </t>
   </si>
   <si>
-    <t xml:space="preserve">Laura Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cajs@justice.gov.uk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henry Goldsack/John Alexander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ed Rowland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anne Kelleher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">communityperformanceenquiries@justice.gov.uk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAJS@justice.gov.uk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Rudling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">criminal_court_sta@justice.gov.uk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fazeen Khamkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CJS_Statistics@justice.gov.uk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrea Solomou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liz Whiting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probation-statistics-enquiries@justice.gov.uk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wincen Lowe</t>
-  </si>
-  <si>
     <t xml:space="preserve">judicial.statistics@justice.gov.uk</t>
   </si>
   <si>
-    <t xml:space="preserve">Helen Fairbanks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saleyah Miah</t>
+    <t xml:space="preserve">Anna Hollywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tara Rose</t>
   </si>
   <si>
     <t xml:space="preserve">ppas_statistics@justice.gov.uk</t>
@@ -1221,13 +1203,10 @@
     <t xml:space="preserve">Arun Mehan</t>
   </si>
   <si>
-    <t xml:space="preserve">Katherine Tatlock / Pete Burgess </t>
+    <t xml:space="preserve">Louisa Hutton-Adams</t>
   </si>
   <si>
     <t xml:space="preserve">Jamie Newton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katherine Tatlock</t>
   </si>
   <si>
     <t xml:space="preserve">YCSInformationAndPerformance@justice.gov.uk</t>
@@ -1866,7 +1845,7 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -1876,185 +1855,173 @@
       <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="B9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I9" s="7"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="E10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="H10" s="6"/>
       <c r="I10" s="7"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="I11" s="7"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="F12" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="6"/>
       <c r="I12" s="7"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="C13" s="6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="I13" s="7"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
       <c r="F14" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
       <c r="I14" s="7"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
       <c r="I15" s="7"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -2062,27 +2029,29 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="6" t="n">
+        <v>15</v>
+      </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="7"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -2090,355 +2059,365 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
+      <c r="E19" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="F19" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
       <c r="F20" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I22" s="7"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I23" s="7"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I24" s="7"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="6" t="s">
         <v>48</v>
       </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
       <c r="I25" s="7"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>45</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
       <c r="F26" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>48</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
       <c r="I26" s="7"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
+      <c r="F27" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="F28" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="I28" s="7"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F29" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>20</v>
-      </c>
       <c r="H29" s="6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="F30" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>61</v>
-      </c>
+      <c r="H30" s="6"/>
       <c r="I30" s="7"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="C31" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I31" s="7"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="D32" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="I32" s="7"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="6" t="s">
         <v>68</v>
       </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
       <c r="I33" s="7"/>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -2452,19 +2431,19 @@
         <v>71</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>72</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="I34" s="7"/>
     </row>
@@ -2472,82 +2451,96 @@
       <c r="A35" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+      <c r="B35" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I35" s="7"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
       <c r="F36" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
       <c r="I36" s="7"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="F37" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G37" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
+      <c r="C38" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="F38" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2561,99 +2554,75 @@
         <v>84</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G39" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="I39" s="7"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
       <c r="I40" s="7"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>90</v>
-      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
       <c r="F41" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
       <c r="I41" s="7"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
+      <c r="F42" s="6" t="n">
+        <v>28</v>
+      </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="7"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -2661,37 +2630,61 @@
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
       <c r="F44" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
+      <c r="C45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F45" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>96</v>
@@ -2700,7 +2693,7 @@
         <v>97</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>98</v>
@@ -2709,16 +2702,16 @@
         <v>30</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>99</v>
@@ -2727,7 +2720,7 @@
         <v>97</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>98</v>
@@ -2736,281 +2729,281 @@
         <v>30</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I48" s="7"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="I49" s="7"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="I50" s="7"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I51" s="7"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="I52" s="7"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="I53" s="7"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>48</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
       <c r="I54" s="7"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>103</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
       <c r="F55" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>46</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
       <c r="I55" s="7"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
+      <c r="F56" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="I56" s="7"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
+      <c r="B57" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>117</v>
+      </c>
       <c r="F57" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="I57" s="7"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B58" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="D58" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="F58" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I58" s="7"/>
     </row>
@@ -3018,53 +3011,41 @@
       <c r="A59" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B59" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>122</v>
-      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
       <c r="F59" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>46</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
       <c r="I59" s="7"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B60" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="F60" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="I60" s="7"/>
     </row>
@@ -3076,9 +3057,7 @@
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
-      <c r="F61" s="6" t="n">
-        <v>34</v>
-      </c>
+      <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="7"/>
@@ -3094,59 +3073,61 @@
         <v>127</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="I62" s="7"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
+      <c r="F63" s="6" t="n">
+        <v>37</v>
+      </c>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
       <c r="I63" s="7"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="D64" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>117</v>
-      </c>
       <c r="F64" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="I64" s="7"/>
     </row>
@@ -3154,300 +3135,298 @@
       <c r="A65" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
+      <c r="B65" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="F65" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
+        <v>39</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I65" s="7"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E66" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="F66" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
       <c r="I66" s="7"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>141</v>
-      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
       <c r="F67" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
       <c r="I67" s="7"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
+      <c r="F68" s="6" t="n">
+        <v>41</v>
+      </c>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
       <c r="I68" s="7"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
+        <v>140</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="F69" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="I69" s="7"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
+      <c r="C70" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>146</v>
+      </c>
       <c r="F70" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I70" s="7"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="I71" s="7"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="D72" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E72" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I72" s="7"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>152</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>155</v>
+        <v>43</v>
       </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="D74" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B75" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="D75" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>48</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
       <c r="I76" s="7"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B77" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="F77" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I77" s="7"/>
     </row>
@@ -3455,94 +3434,96 @@
       <c r="A78" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
+      <c r="B78" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I79" s="7"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B80" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C80" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C80" s="6" t="s">
-        <v>167</v>
-      </c>
       <c r="D80" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I80" s="7"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>147</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
       <c r="F81" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>68</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
       <c r="I81" s="7"/>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3550,216 +3531,202 @@
         <v>169</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C82" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="I82" s="7"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
+      <c r="D83" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>158</v>
+      </c>
       <c r="F83" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I83" s="7"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B84" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>176</v>
-      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
       <c r="I84" s="7"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B85" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="D85" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G85" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="I85" s="7"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
+      <c r="C86" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I86" s="7"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C87" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B87" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>182</v>
-      </c>
       <c r="D87" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G87" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="I87" s="7"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>171</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
       <c r="F88" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
       <c r="I88" s="7"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>171</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
       <c r="F89" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
       <c r="I89" s="7"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
-      <c r="F90" s="6" t="n">
-        <v>51</v>
-      </c>
+      <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
       <c r="I90" s="7"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
@@ -3767,27 +3734,29 @@
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
+      <c r="F92" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
       <c r="I92" s="7"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
       <c r="F93" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
@@ -3795,73 +3764,97 @@
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
       <c r="F94" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I94" s="7"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B95" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
+      <c r="C95" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="F95" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I95" s="7"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B96" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="6" t="s">
-        <v>193</v>
-      </c>
       <c r="C96" s="6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I96" s="7"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>194</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>195</v>
@@ -3870,213 +3863,187 @@
         <v>4</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I97" s="7"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I98" s="7"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I99" s="7"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>46</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
       <c r="I100" s="7"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>195</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
       <c r="F101" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>48</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
       <c r="I101" s="7"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E102" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
+      <c r="F102" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="I102" s="7"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
+      <c r="B103" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="F103" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="I103" s="7"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E104" s="6" t="s">
         <v>208</v>
       </c>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
       <c r="F104" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>46</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
       <c r="I104" s="7"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B105" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>68</v>
-      </c>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
       <c r="I105" s="7"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
@@ -4084,27 +4051,29 @@
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
+      <c r="F107" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="7"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
       <c r="F108" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
@@ -4112,84 +4081,54 @@
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
+        <v>213</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="F109" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I109" s="7"/>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="7"/>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F111" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I111" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:G6"/>
-  <conditionalFormatting sqref="A7:H112">
+  <conditionalFormatting sqref="A7:H110">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>=AND($A7&lt;&gt;$A6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I111">
+  <conditionalFormatting sqref="A7:I109">
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>=LEFT($A7, 3)="MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:H111">
+  <conditionalFormatting sqref="A7:H109">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>=LEFT($A7,3)&lt;&gt;"MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B111">
+  <conditionalFormatting sqref="B7:B109">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>=AND($B7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A111">
+  <conditionalFormatting sqref="A7:A109">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=0,$E7=$E6)</formula>
     </cfRule>
@@ -4197,7 +4136,7 @@
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=1,$E7=$E6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D111">
+  <conditionalFormatting sqref="D7:D109">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>=AND($D7="confirmed")</formula>
     </cfRule>
@@ -4236,17 +4175,16 @@
     <col min="13" max="13" width="30.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="30.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="30.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="30.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -4261,2070 +4199,1953 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="O6" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>236</v>
-      </c>
+      <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
       <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P12" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
       <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P13" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
       <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
       <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>268</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P21" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P22" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
-      <c r="S22" s="13"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P23" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>284</v>
+        <v>232</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P24" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="L25" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="N25" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="M25" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>238</v>
-      </c>
       <c r="O25" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="P25" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>288</v>
+        <v>232</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P26" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
-      <c r="S26" s="13"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>290</v>
+        <v>232</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>291</v>
+        <v>232</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>238</v>
+        <v>286</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="P27" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P28" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
-      <c r="S28" s="13"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P29" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P30" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
-      <c r="S30" s="13"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P31" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="s">
-        <v>238</v>
+        <v>294</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P32" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
-      <c r="S32" s="13"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P33" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
-      <c r="S33" s="13"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P34" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
       <c r="R34" s="13"/>
-      <c r="S34" s="13"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>306</v>
+        <v>232</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P35" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
       <c r="R35" s="13"/>
-      <c r="S35" s="13"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P36" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
-      <c r="S36" s="13"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P37" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
-      <c r="S37" s="13"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>311</v>
+        <v>232</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P38" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="13"/>
-      <c r="S38" s="13"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P39" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="13"/>
-      <c r="S39" s="13"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O40" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P40" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P40" s="13"/>
       <c r="Q40" s="13"/>
       <c r="R40" s="13"/>
-      <c r="S40" s="13"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>238</v>
+        <v>308</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>238</v>
+        <v>309</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>316</v>
+        <v>232</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>317</v>
+        <v>232</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>238</v>
+        <v>311</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O41" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P41" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
       <c r="R41" s="13"/>
-      <c r="S41" s="13"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>238</v>
+        <v>313</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>320</v>
+        <v>232</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>238</v>
+        <v>314</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>321</v>
+        <v>232</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P42" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
       <c r="R42" s="13"/>
-      <c r="S42" s="13"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O43" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P43" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
-      <c r="S43" s="13"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="O44" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="P44" s="12" t="s">
-        <v>238</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="P44" s="13"/>
       <c r="Q44" s="13"/>
       <c r="R44" s="13"/>
-      <c r="S44" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:P6"/>
-  <conditionalFormatting sqref="C7:P44">
+  <autoFilter ref="A6:O6"/>
+  <conditionalFormatting sqref="C7:O44">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>ISNUMBER(SEARCH("confirmed", INDIRECT("RC", FALSE)))</formula>
     </cfRule>
@@ -6360,12 +6181,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -6378,319 +6199,319 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/civil-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C7" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/community-performance-annual-update-to-march-2025", "Link to publication")</f>
       </c>
       <c r="C8" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/coroners-and-burials-statistics", "Link to publication")</f>
       </c>
       <c r="C9" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F9" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>342</v>
-      </c>
       <c r="H9" s="11" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-court-statistics", "Link to publication")</f>
       </c>
       <c r="C10" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C11" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/death-of-offenders-in-the-community", "Link to publication")</f>
       </c>
       <c r="C12" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/diversity-of-the-judiciary-2024-statistics", "Link to publication")</f>
       </c>
       <c r="C13" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/electronic-monitoring-statistics-annual-publication-march-2024", "Link to publication")</f>
       </c>
       <c r="C14" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B15" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/electronic-monitoring-publication", "Link to publication")</f>
       </c>
       <c r="C15" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B16" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/ethnicity-and-the-criminal-justice-system-2024", "Link to publication")</f>
       </c>
       <c r="C16" s="11" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B17" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/family-court-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C17" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6704,337 +6525,337 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B19" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C19" s="11" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B20" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C20" s="11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B21" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-offender-equalities-report", "Link to publication")</f>
       </c>
       <c r="C21" s="11" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C22" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-staff-equalities-report", "Link to publication")</f>
       </c>
       <c r="C23" s="11" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/justice-data-lab", "Link to publication")</f>
       </c>
       <c r="C24" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B25" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/knife-and-offensive-weapon-sentencing-statistics", "Link to publication")</f>
       </c>
       <c r="C25" s="11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B26" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/legal-aid-statistics", "Link to publication")</f>
       </c>
       <c r="C26" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B27" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/mortgage-and-landlord-possession-statistics", "Link to publication")</f>
       </c>
       <c r="C27" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="G27" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="H27" s="11" t="s">
         <v>336</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B28" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/multi-agency-public-protection-arrangements-mappa-annual-reports", "Link to publication")</f>
       </c>
       <c r="C28" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B29" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-accommodation-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C29" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B30" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-employment-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C30" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B31" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-management-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C31" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B32" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -7048,306 +6869,306 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B33" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
       </c>
       <c r="C33" s="11" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B34" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C34" s="11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B35" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
       </c>
       <c r="C35" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B36" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C36" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B37" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
       </c>
       <c r="C37" s="11" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B38" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
       </c>
       <c r="C38" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B39" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
       </c>
       <c r="C39" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B40" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C40" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B41" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
       </c>
       <c r="C41" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="G41" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="H41" s="11" t="s">
         <v>336</v>
-      </c>
-      <c r="H41" s="11" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B42" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
       </c>
       <c r="C42" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B43" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
       </c>
       <c r="C43" s="11" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B44" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
       </c>
       <c r="C44" s="11" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Weekly View)</t>
   </si>
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Last updated:  Thursday 05 March 2026</t>
+    <t xml:space="preserve">Last updated:  Thursday 12 March 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Week Commencing</t>
@@ -55,9 +55,6 @@
     <t xml:space="preserve">March 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 02 Mar 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mon 09 Mar 2026</t>
   </si>
   <si>
@@ -649,6 +646,15 @@
     <t xml:space="preserve">Mon 01 Mar 2027</t>
   </si>
   <si>
+    <t xml:space="preserve">Civil justice statistics quarterly: October to December 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 04 Mar 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 04 Feb 2027</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mon 08 Mar 2027</t>
   </si>
   <si>
@@ -722,6 +728,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thu 03 Dec 2026 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 04 Mar 2027 (provisional)</t>
   </si>
   <si>
     <t xml:space="preserve">Community Performance Annual</t>
@@ -1840,148 +1849,148 @@
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="F8" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I8" s="7"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="E9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="H9" s="6"/>
       <c r="I9" s="7"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="6"/>
       <c r="I10" s="7"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I11" s="7"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I12" s="7"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>28</v>
-      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
       <c r="I13" s="7"/>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1992,9 +2001,7 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="6" t="n">
-        <v>13</v>
-      </c>
+      <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="7"/>
@@ -2007,7 +2014,9 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="F15" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="7"/>
@@ -2021,7 +2030,7 @@
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -2036,7 +2045,7 @@
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -2046,177 +2055,175 @@
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
+      <c r="B18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="F18" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="D19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I22" s="7"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I23" s="7"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
       <c r="I24" s="7"/>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -2227,7 +2234,9 @@
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="7"/>
@@ -2236,338 +2245,336 @@
       <c r="A26" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
+      <c r="B26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="F26" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
+      <c r="H26" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="I26" s="7"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>19</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I28" s="7"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>41</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H29" s="6"/>
       <c r="I29" s="7"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>18</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="I30" s="7"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="I31" s="7"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>41</v>
-      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
       <c r="I32" s="7"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
+      <c r="B33" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I33" s="7"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I34" s="7"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>52</v>
-      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
       <c r="I35" s="7"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
+      <c r="B36" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="F36" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I36" s="7"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>25</v>
       </c>
       <c r="G37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E39" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F39" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
       <c r="I39" s="7"/>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2578,7 +2585,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
+      <c r="F40" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="7"/>
@@ -2592,7 +2601,7 @@
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -2607,7 +2616,7 @@
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -2617,285 +2626,283 @@
       <c r="A43" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
+      <c r="B43" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="F43" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="D44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>99</v>
       </c>
       <c r="C47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>100</v>
       </c>
       <c r="C48" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="I48" s="7"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I49" s="7"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>103</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I50" s="7"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="I51" s="7"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>106</v>
       </c>
       <c r="C52" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I52" s="7"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B53" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>41</v>
-      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
       <c r="I53" s="7"/>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2906,7 +2913,9 @@
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
+      <c r="F54" s="6" t="n">
+        <v>31</v>
+      </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="7"/>
@@ -2915,247 +2924,245 @@
       <c r="A55" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
+      <c r="B55" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="F55" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="I55" s="7"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I56" s="7"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="D57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="I57" s="7"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>117</v>
-      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
       <c r="F58" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>63</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
       <c r="I58" s="7"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
+      <c r="B59" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="F59" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I59" s="7"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F60" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
       <c r="I60" s="7"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+      <c r="B61" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I61" s="7"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
       <c r="F62" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
       <c r="I62" s="7"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
+      <c r="B63" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="F63" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I63" s="7"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F64" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>38</v>
-      </c>
       <c r="G64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I64" s="7"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E65" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F65" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
       <c r="I65" s="7"/>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -3166,7 +3173,9 @@
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
+      <c r="F66" s="6" t="n">
+        <v>40</v>
+      </c>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
       <c r="I66" s="7"/>
@@ -3180,7 +3189,7 @@
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
@@ -3190,488 +3199,488 @@
       <c r="A68" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
+      <c r="B68" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="F68" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="F69" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="I69" s="7"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="I70" s="7"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B71" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="D71" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="I71" s="7"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>151</v>
       </c>
       <c r="C72" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I72" s="7"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>152</v>
       </c>
       <c r="C73" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E73" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>153</v>
       </c>
       <c r="C74" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B75" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
       <c r="I75" s="7"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
+      <c r="B76" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="I76" s="7"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B79" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="D79" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="I79" s="7"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B80" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C80" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>142</v>
-      </c>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
       <c r="F80" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>41</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
       <c r="I80" s="7"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
+      <c r="B81" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="F81" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="I81" s="7"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="I82" s="7"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D83" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F83" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
       <c r="I83" s="7"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
+      <c r="B84" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I84" s="7"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G85" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I85" s="7"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B86" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>180</v>
-      </c>
       <c r="D86" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I86" s="7"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C87" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D87" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>166</v>
-      </c>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
       <c r="F87" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
       <c r="I87" s="7"/>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3683,7 +3692,7 @@
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
@@ -3697,9 +3706,7 @@
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
-      <c r="F89" s="6" t="n">
-        <v>52</v>
-      </c>
+      <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
       <c r="I89" s="7"/>
@@ -3712,7 +3719,9 @@
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
+      <c r="F90" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
       <c r="I90" s="7"/>
@@ -3726,7 +3735,7 @@
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
@@ -3741,7 +3750,7 @@
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
@@ -3751,177 +3760,175 @@
       <c r="A93" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
+      <c r="B93" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="F93" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="I93" s="7"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B94" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="D94" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E94" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I94" s="7"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>191</v>
       </c>
       <c r="C95" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I95" s="7"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>192</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I96" s="7"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I97" s="7"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>196</v>
       </c>
       <c r="C98" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E98" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I98" s="7"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B99" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
       <c r="I99" s="7"/>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3932,7 +3939,9 @@
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
+      <c r="F100" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
       <c r="I100" s="7"/>
@@ -3941,69 +3950,69 @@
       <c r="A101" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
+      <c r="B101" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>202</v>
+      </c>
       <c r="F101" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="I101" s="7"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="I102" s="7"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E103" s="6" t="s">
         <v>207</v>
       </c>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
       <c r="F103" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>63</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
       <c r="I103" s="7"/>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -4014,9 +4023,7 @@
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
-      <c r="F104" s="6" t="n">
-        <v>8</v>
-      </c>
+      <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
       <c r="I104" s="7"/>
@@ -4025,25 +4032,39 @@
       <c r="A105" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
+      <c r="B105" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I105" s="7"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
@@ -4051,14 +4072,14 @@
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
@@ -4066,69 +4087,54 @@
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
+        <v>215</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>217</v>
+      </c>
       <c r="F108" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I108" s="7"/>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F109" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I109" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:G6"/>
-  <conditionalFormatting sqref="A7:H110">
+  <conditionalFormatting sqref="A7:H109">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>=AND($A7&lt;&gt;$A6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I109">
+  <conditionalFormatting sqref="A7:I108">
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>=LEFT($A7, 3)="MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:H109">
+  <conditionalFormatting sqref="A7:H108">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>=LEFT($A7,3)&lt;&gt;"MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B109">
+  <conditionalFormatting sqref="B7:B108">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>=AND($B7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A109">
+  <conditionalFormatting sqref="A7:A108">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=0,$E7=$E6)</formula>
     </cfRule>
@@ -4136,7 +4142,7 @@
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=1,$E7=$E6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D109">
+  <conditionalFormatting sqref="D7:D108">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>=AND($D7="confirmed")</formula>
     </cfRule>
@@ -4179,12 +4185,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -4199,49 +4205,49 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -4249,49 +4255,49 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -4299,49 +4305,49 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -4349,49 +4355,49 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -4399,49 +4405,49 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
@@ -4449,49 +4455,49 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
@@ -4499,49 +4505,49 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
@@ -4549,49 +4555,49 @@
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
@@ -4599,49 +4605,49 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
@@ -4649,49 +4655,49 @@
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
@@ -4699,49 +4705,49 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
@@ -4749,49 +4755,49 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
@@ -4799,47 +4805,47 @@
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
@@ -4847,49 +4853,49 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
@@ -4897,49 +4903,49 @@
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
@@ -4947,49 +4953,49 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
@@ -4997,49 +5003,49 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
@@ -5047,49 +5053,49 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
@@ -5097,49 +5103,49 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
@@ -5147,49 +5153,49 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
@@ -5197,49 +5203,49 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
@@ -5247,49 +5253,49 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -5297,49 +5303,49 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
@@ -5347,49 +5353,49 @@
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
@@ -5397,49 +5403,49 @@
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
@@ -5447,49 +5453,49 @@
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
@@ -5497,47 +5503,47 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -5545,49 +5551,49 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
@@ -5595,49 +5601,49 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
@@ -5645,49 +5651,49 @@
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -5695,49 +5701,49 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
@@ -5745,49 +5751,49 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
@@ -5795,49 +5801,49 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
@@ -5845,49 +5851,49 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
@@ -5895,49 +5901,49 @@
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O40" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P40" s="13"/>
       <c r="Q40" s="13"/>
@@ -5945,49 +5951,49 @@
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O41" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
@@ -5995,49 +6001,49 @@
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
@@ -6045,49 +6051,49 @@
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O43" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
@@ -6095,49 +6101,49 @@
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O44" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P44" s="13"/>
       <c r="Q44" s="13"/>
@@ -6181,12 +6187,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -6199,319 +6205,319 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/civil-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C7" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/community-performance-annual-update-to-march-2025", "Link to publication")</f>
       </c>
       <c r="C8" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>329</v>
-      </c>
       <c r="H8" s="11" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/coroners-and-burials-statistics", "Link to publication")</f>
       </c>
       <c r="C9" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-court-statistics", "Link to publication")</f>
       </c>
       <c r="C10" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C11" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/death-of-offenders-in-the-community", "Link to publication")</f>
       </c>
       <c r="C12" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/diversity-of-the-judiciary-2024-statistics", "Link to publication")</f>
       </c>
       <c r="C13" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/electronic-monitoring-statistics-annual-publication-march-2024", "Link to publication")</f>
       </c>
       <c r="C14" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B15" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/electronic-monitoring-publication", "Link to publication")</f>
       </c>
       <c r="C15" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B16" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/ethnicity-and-the-criminal-justice-system-2024", "Link to publication")</f>
       </c>
       <c r="C16" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>335</v>
-      </c>
       <c r="H16" s="11" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B17" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/family-court-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C17" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6525,337 +6531,337 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B19" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C19" s="11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B20" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C20" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B21" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-offender-equalities-report", "Link to publication")</f>
       </c>
       <c r="C21" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-staff-equalities-report", "Link to publication")</f>
       </c>
       <c r="C23" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/justice-data-lab", "Link to publication")</f>
       </c>
       <c r="C24" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B25" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/knife-and-offensive-weapon-sentencing-statistics", "Link to publication")</f>
       </c>
       <c r="C25" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B26" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/legal-aid-statistics", "Link to publication")</f>
       </c>
       <c r="C26" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B27" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/mortgage-and-landlord-possession-statistics", "Link to publication")</f>
       </c>
       <c r="C27" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B28" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/multi-agency-public-protection-arrangements-mappa-annual-reports", "Link to publication")</f>
       </c>
       <c r="C28" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B29" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-accommodation-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C29" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E29" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="G29" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>329</v>
-      </c>
       <c r="H29" s="11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B30" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-employment-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C30" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E30" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>329</v>
-      </c>
       <c r="H30" s="11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B31" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-management-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C31" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B32" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6869,306 +6875,306 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B33" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
       </c>
       <c r="C33" s="11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B34" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C34" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B35" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
       </c>
       <c r="C35" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B36" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C36" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B37" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
       </c>
       <c r="C37" s="11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B38" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
       </c>
       <c r="C38" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B39" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
       </c>
       <c r="C39" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B40" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C40" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B41" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
       </c>
       <c r="C41" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B42" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
       </c>
       <c r="C42" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B43" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
       </c>
       <c r="C43" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E43" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="G43" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="F43" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>335</v>
-      </c>
       <c r="H43" s="11" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B44" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
       </c>
       <c r="C44" s="11" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Weekly View)</t>
   </si>
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Last updated:  Thursday 12 March 2026</t>
+    <t xml:space="preserve">Last updated:  Thursday 19 March 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Week Commencing</t>
@@ -55,19 +55,22 @@
     <t xml:space="preserve">March 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 09 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tribunals statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 12 Mar 2026</t>
+    <t xml:space="preserve">Mon 16 Mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 23 Mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal aid statistics quarterly: October to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 26 Mar 2026</t>
   </si>
   <si>
     <t xml:space="preserve">confirmed</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 12 Feb 2026</t>
+    <t xml:space="preserve">Thu 26 Feb 2026</t>
   </si>
   <si>
     <t xml:space="preserve">standard</t>
@@ -76,30 +79,6 @@
     <t xml:space="preserve">Mar, Jun, Sep, Dec </t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 16 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pathways between probation and addiction treatment in England: a follow up study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 19 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 19 Feb 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 23 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal aid statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 26 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 26 Feb 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Family court statistics quarterly: October to December 2025</t>
   </si>
   <si>
@@ -904,12 +883,6 @@
     <t xml:space="preserve">Thu 29 Oct 2026 (provisional)</t>
   </si>
   <si>
-    <t xml:space="preserve">pathways between probation and addiction treatment in england</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 19 Mar 2026 (confirmed)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prison Education and Accredited Programme Statistics</t>
   </si>
   <si>
@@ -947,9 +920,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tribunals statistics quarterly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 12 Mar 2026 (confirmed)</t>
   </si>
   <si>
     <t xml:space="preserve">Thu 11 Jun 2026 (provisional)</t>
@@ -1849,173 +1819,151 @@
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
       <c r="I8" s="7"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="6"/>
       <c r="I9" s="7"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10" s="7"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I11" s="7"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>27</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="7"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="6" t="n">
-        <v>13</v>
-      </c>
+      <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="7"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="7"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -2023,14 +1971,14 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -2038,233 +1986,245 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="F17" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I22" s="7"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
       <c r="I23" s="7"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="F24" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="7"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="F25" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="I25" s="7"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I26" s="7"/>
     </row>
@@ -2273,78 +2233,78 @@
         <v>49</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>52</v>
       </c>
       <c r="F27" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="H27" s="6" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>40</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="7"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -2352,241 +2312,229 @@
         <v>56</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="I30" s="7"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>40</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
       <c r="I31" s="7"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I32" s="7"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I33" s="7"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>51</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
       <c r="F34" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
       <c r="I34" s="7"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="F35" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I35" s="7"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>25</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I36" s="7"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="D37" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
       <c r="I38" s="7"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
+      <c r="F39" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="7"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -2594,14 +2542,14 @@
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -2609,572 +2557,572 @@
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="F42" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="D44" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D45" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D46" s="6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D47" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D48" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I48" s="7"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D49" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I49" s="7"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D50" s="6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="I50" s="7"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D51" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I51" s="7"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>40</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
       <c r="I52" s="7"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
+      <c r="F53" s="6" t="n">
+        <v>31</v>
+      </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="7"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>105</v>
+      </c>
       <c r="F54" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="I54" s="7"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="F55" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I55" s="7"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I56" s="7"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>116</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
       <c r="F57" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>62</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
       <c r="I57" s="7"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
+        <v>112</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="F58" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I58" s="7"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
       <c r="I59" s="7"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
+        <v>117</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I60" s="7"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>111</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
       <c r="F61" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
       <c r="I61" s="7"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="F62" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I62" s="7"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="F63" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I63" s="7"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
       <c r="I64" s="7"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
+      <c r="F65" s="6" t="n">
+        <v>40</v>
+      </c>
       <c r="G65" s="6"/>
       <c r="H65" s="6"/>
       <c r="I65" s="7"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
       <c r="F66" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
@@ -3182,502 +3130,502 @@
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
+        <v>132</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>123</v>
+      </c>
       <c r="F67" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="I67" s="7"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="I69" s="7"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="I70" s="7"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I71" s="7"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I72" s="7"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C74" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F74" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
       <c r="I74" s="7"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
+        <v>148</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B76" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="F76" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="I76" s="7"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>141</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
       <c r="F79" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
       <c r="I79" s="7"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
+        <v>161</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>148</v>
+      </c>
       <c r="F80" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="I80" s="7"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="I81" s="7"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
       <c r="I82" s="7"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
+        <v>167</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I83" s="7"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I84" s="7"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>50</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I85" s="7"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>165</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
       <c r="F86" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
       <c r="I86" s="7"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
@@ -3685,42 +3633,42 @@
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
-      <c r="F88" s="6" t="n">
-        <v>52</v>
-      </c>
+      <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
       <c r="I88" s="7"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
+      <c r="F89" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
       <c r="I89" s="7"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
       <c r="F90" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
@@ -3728,14 +3676,14 @@
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
@@ -3743,328 +3691,328 @@
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
+        <v>179</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>182</v>
+      </c>
       <c r="F92" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I92" s="7"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I93" s="7"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I94" s="7"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B95" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D95" s="6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I95" s="7"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I96" s="7"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I97" s="7"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
       <c r="I98" s="7"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
+      <c r="F99" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
       <c r="I99" s="7"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>195</v>
+      </c>
       <c r="F100" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="I100" s="7"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E101" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B101" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="F101" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I101" s="7"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E102" s="6" t="s">
-        <v>206</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
       <c r="F102" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>62</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
       <c r="I102" s="7"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
-      <c r="F103" s="6" t="n">
-        <v>8</v>
-      </c>
+      <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
       <c r="I103" s="7"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
+        <v>202</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I104" s="7"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>212</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
       <c r="F105" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
       <c r="I105" s="7"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
@@ -4072,69 +4020,54 @@
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
+        <v>208</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="F107" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I107" s="7"/>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F108" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I108" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:G6"/>
-  <conditionalFormatting sqref="A7:H109">
+  <conditionalFormatting sqref="A7:H108">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>=AND($A7&lt;&gt;$A6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I108">
+  <conditionalFormatting sqref="A7:I107">
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>=LEFT($A7, 3)="MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:H108">
+  <conditionalFormatting sqref="A7:H107">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>=LEFT($A7,3)&lt;&gt;"MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B108">
+  <conditionalFormatting sqref="B7:B107">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>=AND($B7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A108">
+  <conditionalFormatting sqref="A7:A107">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=0,$E7=$E6)</formula>
     </cfRule>
@@ -4142,7 +4075,7 @@
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=1,$E7=$E6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D108">
+  <conditionalFormatting sqref="D7:D107">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>=AND($D7="confirmed")</formula>
     </cfRule>
@@ -4185,12 +4118,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -4205,49 +4138,49 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="O6" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>232</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -4255,49 +4188,49 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -4305,49 +4238,49 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -4355,49 +4288,49 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -4405,49 +4338,49 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
@@ -4455,49 +4388,49 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
@@ -4505,49 +4438,49 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
@@ -4555,49 +4488,49 @@
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
@@ -4605,49 +4538,49 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
@@ -4655,49 +4588,49 @@
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
@@ -4705,49 +4638,49 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
@@ -4755,49 +4688,49 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
@@ -4805,47 +4738,47 @@
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
@@ -4853,49 +4786,49 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
@@ -4903,49 +4836,49 @@
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
@@ -4953,49 +4886,49 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
@@ -5003,49 +4936,49 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
@@ -5053,49 +4986,49 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
@@ -5103,49 +5036,49 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
@@ -5153,49 +5086,49 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K25" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="N25" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="L25" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>282</v>
-      </c>
       <c r="O25" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
@@ -5203,49 +5136,49 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
@@ -5253,49 +5186,49 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -5303,49 +5236,49 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
@@ -5353,49 +5286,49 @@
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
@@ -5403,49 +5336,49 @@
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
@@ -5453,49 +5386,49 @@
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
@@ -5503,47 +5436,49 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="B32" s="11"/>
+        <v>289</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>290</v>
+      </c>
       <c r="C32" s="12" t="s">
-        <v>297</v>
+        <v>227</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -5551,49 +5486,49 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>299</v>
+        <v>87</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
@@ -5601,49 +5536,49 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
@@ -5651,49 +5586,49 @@
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>302</v>
+        <v>227</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -5701,49 +5636,49 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>42</v>
+        <v>296</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
@@ -5751,49 +5686,49 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
@@ -5801,49 +5736,49 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
@@ -5851,49 +5786,49 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
@@ -5901,49 +5836,49 @@
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>234</v>
+        <v>302</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O40" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P40" s="13"/>
       <c r="Q40" s="13"/>
@@ -5951,49 +5886,49 @@
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>311</v>
+        <v>227</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>234</v>
+        <v>306</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>312</v>
+        <v>227</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>313</v>
+        <v>227</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>314</v>
+        <v>227</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O41" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
@@ -6001,49 +5936,49 @@
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>53</v>
+        <v>253</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>317</v>
+        <v>227</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
@@ -6051,107 +5986,57 @@
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="O43" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="J44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="K44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="M44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="N44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="O44" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="13"/>
-      <c r="R44" s="13"/>
-    </row>
   </sheetData>
   <autoFilter ref="A6:O6"/>
-  <conditionalFormatting sqref="C7:O44">
+  <conditionalFormatting sqref="C7:O43">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>ISNUMBER(SEARCH("confirmed", INDIRECT("RC", FALSE)))</formula>
     </cfRule>
@@ -6187,12 +6072,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -6205,319 +6090,319 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/civil-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C7" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/community-performance-annual-update-to-march-2025", "Link to publication")</f>
       </c>
       <c r="C8" s="11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/coroners-and-burials-statistics", "Link to publication")</f>
       </c>
       <c r="C9" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>329</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-court-statistics", "Link to publication")</f>
       </c>
       <c r="C10" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="G10" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>332</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C11" s="11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/death-of-offenders-in-the-community", "Link to publication")</f>
       </c>
       <c r="C12" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/diversity-of-the-judiciary-2024-statistics", "Link to publication")</f>
       </c>
       <c r="C13" s="11" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/electronic-monitoring-statistics-annual-publication-march-2024", "Link to publication")</f>
       </c>
       <c r="C14" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B15" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/electronic-monitoring-publication", "Link to publication")</f>
       </c>
       <c r="C15" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B16" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/ethnicity-and-the-criminal-justice-system-2024", "Link to publication")</f>
       </c>
       <c r="C16" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B17" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/family-court-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C17" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6531,650 +6416,636 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B19" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C19" s="11" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B20" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C20" s="11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B21" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-offender-equalities-report", "Link to publication")</f>
       </c>
       <c r="C21" s="11" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C22" s="11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-staff-equalities-report", "Link to publication")</f>
       </c>
       <c r="C23" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/justice-data-lab", "Link to publication")</f>
       </c>
       <c r="C24" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B25" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/knife-and-offensive-weapon-sentencing-statistics", "Link to publication")</f>
       </c>
       <c r="C25" s="11" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B26" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/legal-aid-statistics", "Link to publication")</f>
       </c>
       <c r="C26" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B27" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/mortgage-and-landlord-possession-statistics", "Link to publication")</f>
       </c>
       <c r="C27" s="11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B28" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/multi-agency-public-protection-arrangements-mappa-annual-reports", "Link to publication")</f>
       </c>
       <c r="C28" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B29" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-accommodation-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C29" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B30" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-employment-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C30" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B31" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-management-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C31" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B32" s="17" t="str">
-        <f>HYPERLINK("NA", "Link to publication")</f>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B33" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C33" s="11" t="s">
-        <v>299</v>
+        <v>87</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>364</v>
+        <v>325</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B34" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
       </c>
       <c r="C34" s="11" t="s">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B35" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C35" s="11" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>389</v>
+        <v>336</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B36" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
       </c>
       <c r="C36" s="11" t="s">
-        <v>42</v>
+        <v>296</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>391</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B37" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
       </c>
       <c r="C37" s="11" t="s">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
+        <v>384</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="G37" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B38" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
       </c>
       <c r="C38" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B39" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C39" s="11" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>398</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>397</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="11" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B40" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
       </c>
       <c r="C40" s="11" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
+        <v>391</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>321</v>
+      </c>
       <c r="G40" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>400</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B41" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
       </c>
       <c r="C41" s="11" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>339</v>
+        <v>392</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B42" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
       </c>
       <c r="C42" s="11" t="s">
-        <v>53</v>
+        <v>253</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>402</v>
+        <v>334</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B43" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
       </c>
       <c r="C43" s="11" t="s">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="B44" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="396">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Weekly View)</t>
   </si>
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Last updated:  Thursday 19 March 2026</t>
+    <t xml:space="preserve">Last updated:  Thursday 26 March 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Week Commencing</t>
@@ -55,13 +55,10 @@
     <t xml:space="preserve">March 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 16 Mar 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mon 23 Mar 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Legal aid statistics quarterly: October to December 2025</t>
+    <t xml:space="preserve">Criminal court statistics quarterly: October to December 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Thu 26 Mar 2026</t>
@@ -79,12 +76,6 @@
     <t xml:space="preserve">Mar, Jun, Sep, Dec </t>
   </si>
   <si>
-    <t xml:space="preserve">Family court statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criminal court statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mon 30 Mar 2026</t>
   </si>
   <si>
@@ -100,6 +91,15 @@
     <t xml:space="preserve">Mon 20 Apr 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Electronic Monitoring Statistics Publication, March 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 23 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan, Apr, Jul, Oct </t>
+  </si>
+  <si>
     <t xml:space="preserve">Mon 27 Apr 2026</t>
   </si>
   <si>
@@ -109,33 +109,30 @@
     <t xml:space="preserve">Thu 30 Apr 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Thu 02 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb, May, Aug,Nov </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety in the Children and Young People Secure Estate: Update to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety in custody: quarterly update to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offender management statistics quarterly: October to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proven reoffending statistics: April to June 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justice data lab statistics: April 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">provisional</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 02 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb, May, Aug,Nov </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safety in the Children and Young People Secure Estate: Update to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan, Apr, Jul, Oct </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safety in custody: quarterly update to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offender management statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proven reoffending statistics: April to June 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justice data lab statistics: April 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">May 2026</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t xml:space="preserve">Thu 21 May 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 23 Apr 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">First time entrants (FTE) and Offender Histories: 2025</t>
   </si>
   <si>
@@ -742,93 +736,99 @@
     <t xml:space="preserve">Criminal Justice statistics quarterly</t>
   </si>
   <si>
+    <t xml:space="preserve">Thu 30 Apr 2026 (confirmed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 30 Jul 2026 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 22 Oct 2026 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 28 Jan 2027 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deaths of offenders supervised in the community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 29 Oct 2026 (confirmed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diversity of the judiciary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">July </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronic Monitoring Statistics Annual Publication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronic Monitoring Statistics Publication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 23 Apr 2026 (confirmed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethnicity and the Criminal Justice System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family court statistics quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 25 Jun 2026 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 24 Sep 2026 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 25 Mar 2027 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first time entrants (fte) and offender histories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 21 May 2026 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First time entrants (FTE) into the Criminal Justice System and Offender Histories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMPPS Annual Digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMPPS offender equalities report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nov </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMPPS workforce quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 21 May 2026 (confirmed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 20 Aug 2026 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 19 Nov 2026 (provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMPPS Staff Equalities Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justice data lab statistics</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thu 30 Apr 2026 (provisional)</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 30 Jul 2026 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 22 Oct 2026 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 28 Jan 2027 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deaths of offenders supervised in the community</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 29 Oct 2026 (confirmed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diversity of the judiciary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">July </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronic Monitoring Statistics Annual Publication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronic Monitoring Statistics Publication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethnicity and the Criminal Justice System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Family court statistics quarterly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 25 Jun 2026 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 24 Sep 2026 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 25 Mar 2027 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first time entrants (fte) and offender histories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 21 May 2026 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First time entrants (FTE) into the Criminal Justice System and Offender Histories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMPPS Annual Digest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMPPS offender equalities report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMPPS workforce quarterly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 21 May 2026 (confirmed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 20 Aug 2026 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 19 Nov 2026 (provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMPPS Staff Equalities Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justice data lab statistics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fri 31 Jul 2026 (provisional)</t>
   </si>
   <si>
@@ -875,9 +875,6 @@
   </si>
   <si>
     <t xml:space="preserve">Offender management statistics quarterly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 30 Apr 2026 (confirmed)</t>
   </si>
   <si>
     <t xml:space="preserve">Thu 29 Oct 2026 (provisional)</t>
@@ -1819,96 +1816,70 @@
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="F8" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I8" s="7"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
       <c r="I9" s="7"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
       <c r="I10" s="7"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
       <c r="I11" s="7"/>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1920,7 +1891,7 @@
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -1930,58 +1901,108 @@
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="I13" s="7"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="F14" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I14" s="7"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="F15" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="I15" s="7"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
       <c r="I16" s="7"/>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1989,25 +2010,25 @@
         <v>28</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -2016,25 +2037,25 @@
         <v>28</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I18" s="7"/>
     </row>
@@ -2043,1574 +2064,1536 @@
         <v>28</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>35</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
       <c r="I20" s="7"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>32</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
       <c r="F21" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>35</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
       <c r="I21" s="7"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I22" s="7"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I23" s="7"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+      <c r="H24" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I24" s="7"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>46</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H25" s="6"/>
       <c r="I25" s="7"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I26" s="7"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="7"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="I30" s="7"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
+      <c r="F31" s="6" t="n">
+        <v>24</v>
+      </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="7"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I32" s="7"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I33" s="7"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="F34" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I34" s="7"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
       <c r="I35" s="7"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
       <c r="F36" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
       <c r="I36" s="7"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
       <c r="I37" s="7"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
+      <c r="F38" s="6" t="n">
+        <v>29</v>
+      </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="7"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="F39" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
       <c r="I39" s="7"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
+      <c r="B40" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="F40" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="I40" s="7"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="F41" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="I48" s="7"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>97</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
       <c r="I49" s="7"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D50" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
       <c r="I50" s="7"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I51" s="7"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
+        <v>104</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I52" s="7"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
+        <v>104</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>107</v>
+      </c>
       <c r="F53" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="I53" s="7"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>105</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
       <c r="F54" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>33</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
       <c r="I54" s="7"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="I55" s="7"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>55</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
       <c r="I56" s="7"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
+        <v>115</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="F57" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I57" s="7"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>115</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
       <c r="F58" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
       <c r="I58" s="7"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I59" s="7"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I60" s="7"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
-      <c r="F61" s="6" t="n">
-        <v>37</v>
-      </c>
+      <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="7"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>124</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
       <c r="F62" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
       <c r="I62" s="7"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>128</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
       <c r="F63" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
       <c r="I63" s="7"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
+        <v>130</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I64" s="7"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
+        <v>133</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="F65" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="I65" s="7"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
+        <v>133</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>139</v>
+      </c>
       <c r="F66" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>140</v>
+      </c>
       <c r="I66" s="7"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I67" s="7"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B69" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="I69" s="7"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I70" s="7"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>35</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
       <c r="I71" s="7"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I72" s="7"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
+        <v>154</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>155</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
       <c r="F76" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>33</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
       <c r="I76" s="7"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
-      <c r="F79" s="6" t="n">
-        <v>47</v>
-      </c>
+      <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
       <c r="I79" s="7"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I80" s="7"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G81" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H81" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="I81" s="7"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
+        <v>168</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I82" s="7"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>154</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
       <c r="F83" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
       <c r="I83" s="7"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C84" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>158</v>
-      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
       <c r="F84" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
       <c r="I84" s="7"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
       <c r="I85" s="7"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
@@ -3618,14 +3601,14 @@
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
@@ -3633,247 +3616,273 @@
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
+      <c r="F88" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
       <c r="I88" s="7"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
+        <v>177</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="F89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="I89" s="7"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
+      <c r="B90" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="F90" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="I90" s="7"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
+        <v>177</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="F91" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="I91" s="7"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I92" s="7"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B93" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>181</v>
-      </c>
       <c r="D93" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I93" s="7"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>181</v>
-      </c>
       <c r="D94" s="6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I94" s="7"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F95" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>35</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
       <c r="I95" s="7"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>182</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
       <c r="F96" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>33</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
       <c r="I96" s="7"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I97" s="7"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
+        <v>194</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="I98" s="7"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
       <c r="F99" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
@@ -3881,68 +3890,54 @@
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>33</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
       <c r="I100" s="7"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G101" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I101" s="7"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
@@ -3950,124 +3945,69 @@
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
+      <c r="F103" s="6" t="n">
+        <v>11</v>
+      </c>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
       <c r="I103" s="7"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H104" s="6" t="s">
-        <v>20</v>
-      </c>
       <c r="I104" s="7"/>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="7"/>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="7"/>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F107" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I107" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:G6"/>
-  <conditionalFormatting sqref="A7:H108">
+  <conditionalFormatting sqref="A7:H105">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>=AND($A7&lt;&gt;$A6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I107">
+  <conditionalFormatting sqref="A7:I104">
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>=LEFT($A7, 3)="MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:H107">
+  <conditionalFormatting sqref="A7:H104">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>=LEFT($A7,3)&lt;&gt;"MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B107">
+  <conditionalFormatting sqref="B7:B104">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>=AND($B7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A107">
+  <conditionalFormatting sqref="A7:A104">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=0,$E7=$E6)</formula>
     </cfRule>
@@ -4075,7 +4015,7 @@
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=1,$E7=$E6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D107">
+  <conditionalFormatting sqref="D7:D104">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>=AND($D7="confirmed")</formula>
     </cfRule>
@@ -4118,12 +4058,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -4138,49 +4078,49 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="O6" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>225</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -4188,49 +4128,49 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="G7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="J7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L7" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I7" s="12" t="s">
+      <c r="M7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="O7" s="12" t="s">
         <v>229</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>231</v>
       </c>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -4238,49 +4178,49 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -4288,49 +4228,49 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -4338,49 +4278,49 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="12" t="s">
+      <c r="G10" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="J10" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L10" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>240</v>
-      </c>
       <c r="M10" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
@@ -4388,49 +4328,49 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="H11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G11" s="12" t="s">
+      <c r="K11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="M11" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>245</v>
-      </c>
       <c r="N11" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
@@ -4438,49 +4378,49 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
@@ -4488,49 +4428,49 @@
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
@@ -4538,49 +4478,49 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
@@ -4588,49 +4528,49 @@
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
@@ -4638,49 +4578,49 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>253</v>
-      </c>
       <c r="C16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
@@ -4688,49 +4628,49 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F17" s="12" t="s">
+      <c r="G17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I17" s="12" t="s">
+      <c r="J17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="O17" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>257</v>
       </c>
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
@@ -4738,47 +4678,47 @@
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
@@ -4786,49 +4726,49 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>261</v>
-      </c>
       <c r="C19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
@@ -4836,49 +4776,49 @@
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
@@ -4886,49 +4826,49 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>264</v>
-      </c>
       <c r="C21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
@@ -4936,49 +4876,49 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E22" s="12" t="s">
+      <c r="F22" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H22" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H22" s="12" t="s">
+      <c r="I22" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K22" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="I22" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>268</v>
-      </c>
       <c r="L22" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
@@ -4986,49 +4926,49 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
@@ -5036,49 +4976,49 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>242</v>
-      </c>
       <c r="E24" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>271</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J24" s="12" t="s">
         <v>272</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>273</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
@@ -5089,46 +5029,46 @@
         <v>274</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H25" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K25" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="I25" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>268</v>
-      </c>
       <c r="L25" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N25" s="12" t="s">
         <v>275</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
@@ -5139,46 +5079,46 @@
         <v>276</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>277</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
@@ -5189,46 +5129,46 @@
         <v>278</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>279</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>280</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K27" s="12" t="s">
         <v>281</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N27" s="12" t="s">
         <v>282</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -5239,46 +5179,46 @@
         <v>283</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
@@ -5289,46 +5229,46 @@
         <v>284</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
@@ -5339,46 +5279,46 @@
         <v>285</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
@@ -5389,46 +5329,46 @@
         <v>286</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D31" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J31" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G31" s="12" t="s">
+      <c r="K31" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="M31" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="H31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="M31" s="12" t="s">
-        <v>245</v>
-      </c>
       <c r="N31" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
@@ -5436,49 +5376,49 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>290</v>
-      </c>
       <c r="C32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -5486,49 +5426,49 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>271</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
@@ -5536,49 +5476,49 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K34" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K34" s="12" t="s">
-        <v>293</v>
-      </c>
       <c r="L34" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
@@ -5586,49 +5526,49 @@
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D35" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J35" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="E35" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G35" s="12" t="s">
+      <c r="K35" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="M35" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="H35" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="K35" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L35" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="M35" s="12" t="s">
-        <v>245</v>
-      </c>
       <c r="N35" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -5636,49 +5576,49 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B36" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>296</v>
-      </c>
       <c r="C36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
@@ -5686,49 +5626,49 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="M37" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="M37" s="12" t="s">
-        <v>298</v>
-      </c>
       <c r="N37" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
@@ -5736,49 +5676,49 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D38" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J38" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="E38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G38" s="12" t="s">
+      <c r="K38" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="M38" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="H38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="M38" s="12" t="s">
-        <v>245</v>
-      </c>
       <c r="N38" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
@@ -5786,49 +5726,49 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
@@ -5836,49 +5776,49 @@
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F40" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F40" s="12" t="s">
+      <c r="G40" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I40" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="G40" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I40" s="12" t="s">
+      <c r="J40" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L40" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="J40" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K40" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>304</v>
-      </c>
       <c r="M40" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O40" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P40" s="13"/>
       <c r="Q40" s="13"/>
@@ -5886,49 +5826,49 @@
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E41" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E41" s="12" t="s">
+      <c r="F41" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K41" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="F41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>307</v>
-      </c>
       <c r="L41" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O41" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
@@ -5936,49 +5876,49 @@
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
@@ -5986,49 +5926,49 @@
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>310</v>
-      </c>
       <c r="C43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O43" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
@@ -6072,12 +6012,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -6090,319 +6030,319 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="10" t="s">
         <v>317</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/civil-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C7" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="H7" s="11" t="s">
         <v>322</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/community-performance-annual-update-to-march-2025", "Link to publication")</f>
       </c>
       <c r="C8" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D8" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>326</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/coroners-and-burials-statistics", "Link to publication")</f>
       </c>
       <c r="C9" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>321</v>
-      </c>
       <c r="G9" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>328</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-court-statistics", "Link to publication")</f>
       </c>
       <c r="C10" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F10" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>331</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>333</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/death-of-offenders-in-the-community", "Link to publication")</f>
       </c>
       <c r="C12" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H12" s="11" t="s">
         <v>336</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/diversity-of-the-judiciary-2024-statistics", "Link to publication")</f>
       </c>
       <c r="C13" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D13" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F13" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>339</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/electronic-monitoring-statistics-annual-publication-march-2024", "Link to publication")</f>
       </c>
       <c r="C14" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D14" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="F14" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>342</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B15" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/electronic-monitoring-publication", "Link to publication")</f>
       </c>
       <c r="C15" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D15" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="F15" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>342</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B16" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/ethnicity-and-the-criminal-justice-system-2024", "Link to publication")</f>
       </c>
       <c r="C16" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>333</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B17" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/family-court-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C17" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>344</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6416,154 +6356,154 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B19" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C19" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D19" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="F19" s="11" t="s">
+      <c r="G19" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H19" s="11" t="s">
         <v>347</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B20" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C20" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D20" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="F20" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="G20" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H20" s="11" t="s">
         <v>351</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B21" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-offender-equalities-report", "Link to publication")</f>
       </c>
       <c r="C21" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D21" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="F21" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H21" s="11" t="s">
         <v>354</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C22" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-staff-equalities-report", "Link to publication")</f>
       </c>
       <c r="C23" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/justice-data-lab", "Link to publication")</f>
       </c>
       <c r="C24" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D24" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="F24" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>359</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -6574,22 +6514,22 @@
         <f>HYPERLINK("https://www.gov.uk/government/collections/knife-and-offensive-weapon-sentencing-statistics", "Link to publication")</f>
       </c>
       <c r="C25" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F25" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H25" s="11" t="s">
         <v>347</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -6600,22 +6540,22 @@
         <f>HYPERLINK("https://www.gov.uk/government/collections/legal-aid-statistics", "Link to publication")</f>
       </c>
       <c r="C26" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D26" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="F26" s="11" t="s">
+      <c r="G26" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>363</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -6626,22 +6566,22 @@
         <f>HYPERLINK("https://www.gov.uk/government/collections/mortgage-and-landlord-possession-statistics", "Link to publication")</f>
       </c>
       <c r="C27" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F27" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="G27" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="G27" s="11" t="s">
-        <v>322</v>
-      </c>
       <c r="H27" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -6652,18 +6592,18 @@
         <f>HYPERLINK("https://www.gov.uk/government/collections/multi-agency-public-protection-arrangements-mappa-annual-reports", "Link to publication")</f>
       </c>
       <c r="C28" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -6674,22 +6614,22 @@
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-accommodation-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C29" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="F29" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="F29" s="11" t="s">
+      <c r="G29" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H29" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -6700,22 +6640,22 @@
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-employment-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C30" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D30" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="F30" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="F30" s="11" t="s">
+      <c r="G30" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -6726,326 +6666,326 @@
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-management-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C31" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D31" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="F31" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="G31" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H31" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B32" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
       </c>
       <c r="C32" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D32" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E32" s="11" t="s">
-        <v>354</v>
-      </c>
       <c r="F32" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B33" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C33" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D33" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="E33" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="F33" s="11" t="s">
+      <c r="G33" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H33" s="11" t="s">
         <v>376</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B34" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
       </c>
       <c r="C34" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D34" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="F34" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H34" s="11" t="s">
         <v>379</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B35" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C35" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D35" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="H35" s="11" t="s">
         <v>381</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B36" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
       </c>
       <c r="C36" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B37" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
       </c>
       <c r="C37" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D37" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="F37" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="F37" s="11" t="s">
-        <v>386</v>
-      </c>
       <c r="G37" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B38" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
       </c>
       <c r="C38" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="F38" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H38" s="11" t="s">
         <v>388</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B39" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C39" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B40" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
       </c>
       <c r="C40" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E40" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="F40" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="G40" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="G40" s="11" t="s">
-        <v>322</v>
-      </c>
       <c r="H40" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B41" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
       </c>
       <c r="C41" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D41" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="E41" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>369</v>
-      </c>
       <c r="G41" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B42" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
       </c>
       <c r="C42" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D42" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H42" s="11" t="s">
         <v>333</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B43" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
       </c>
       <c r="C43" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D43" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="F43" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="G43" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H43" s="11" t="s">
         <v>395</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Weekly View)</t>
   </si>
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Last updated:  Thursday 26 March 2026</t>
+    <t xml:space="preserve">Last updated:  Thursday 02 April 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Week Commencing</t>
@@ -55,156 +55,150 @@
     <t xml:space="preserve">March 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 23 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criminal court statistics quarterly: October to December 2025</t>
+    <t xml:space="preserve">Mon 30 Mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 06 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 13 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 20 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronic Monitoring Statistics Publication, March 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 23 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confirmed</t>
   </si>
   <si>
     <t xml:space="preserve">Thu 26 Mar 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 26 Feb 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">standard</t>
   </si>
   <si>
+    <t xml:space="preserve">Jan, Apr, Jul, Oct </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prison leavers in substance misuse treatment: 4-week outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 27 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criminal Justice Statistics Quarterly: December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 30 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 02 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb, May, Aug,Nov </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety in the Children and Young People Secure Estate: Update to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety in custody: quarterly update to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offender management statistics quarterly: October to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proven reoffending statistics: April to June 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justice data lab statistics: April 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 04 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 11 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unpaid work management information, update to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 14 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 16 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May, Nov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coroners statistics 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">provisional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 18 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HM Prison &amp; Probation Service workforce quarterly: March 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 21 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First time entrants (FTE) and Offender Histories: 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knife and Offensive Weapon Sentencing Statistics: October to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb, May, Aug, Nov </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 25 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage and landlord possession statistics: January to March 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sun 31 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sun 03 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">June 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 01 Jun 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil justice statistics quarterly: January to March 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 04 Jun 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 07 May 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mar, Jun, Sep, Dec </t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 30 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">April 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 06 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 13 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 20 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronic Monitoring Statistics Publication, March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 23 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan, Apr, Jul, Oct </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 27 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criminal Justice Statistics Quarterly: December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 30 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 02 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb, May, Aug,Nov </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safety in the Children and Young People Secure Estate: Update to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safety in custody: quarterly update to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offender management statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proven reoffending statistics: April to June 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justice data lab statistics: April 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">provisional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 04 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 11 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unpaid work management information, update to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 14 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 16 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May, Nov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coroners statistics 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 18 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HM Prison &amp; Probation Service workforce quarterly: March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 21 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First time entrants (FTE) and Offender Histories: 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knife and Offensive Weapon Sentencing Statistics: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb, May, Aug, Nov </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 25 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortgage and landlord possession statistics: January to March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun 31 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun 03 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">June 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 01 Jun 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Civil justice statistics quarterly: January to March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 04 Jun 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 07 May 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mon 08 Jun 2026</t>
   </si>
   <si>
@@ -310,6 +304,9 @@
     <t xml:space="preserve">Criminal Justice Statistics Quarterly: March 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">HMPPS Annual Digest, April 2025 to March 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">August 2026</t>
   </si>
   <si>
@@ -493,6 +490,21 @@
     <t xml:space="preserve">Mon 23 Nov 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">HM Prison and Probation Service Offender Equalities Report: 2025 to 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 26 Nov 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nov </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prison Education and Accredited Programme Statistics 2025 to 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mon 30 Nov 2026</t>
   </si>
   <si>
@@ -652,9 +664,6 @@
     <t xml:space="preserve">Publication series</t>
   </si>
   <si>
-    <t xml:space="preserve">Mar 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apr 2026</t>
   </si>
   <si>
@@ -721,9 +730,6 @@
     <t xml:space="preserve">Criminal court statistics quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 26 Mar 2026 (confirmed)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tue 30 Jun 2026 (provisional)</t>
   </si>
   <si>
@@ -805,7 +811,7 @@
     <t xml:space="preserve">HMPPS offender equalities report</t>
   </si>
   <si>
-    <t xml:space="preserve">Nov </t>
+    <t xml:space="preserve">Thu 26 Nov 2026 (provisional)</t>
   </si>
   <si>
     <t xml:space="preserve">HMPPS workforce quarterly</t>
@@ -826,9 +832,6 @@
     <t xml:space="preserve">Justice data lab statistics</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 30 Apr 2026 (provisional)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fri 31 Jul 2026 (provisional)</t>
   </si>
   <si>
@@ -883,7 +886,7 @@
     <t xml:space="preserve">Prison Education and Accredited Programme Statistics</t>
   </si>
   <si>
-    <t xml:space="preserve">Sep</t>
+    <t xml:space="preserve">prison leavers in substance misuse treatment</t>
   </si>
   <si>
     <t xml:space="preserve">Prison Performance Ratings</t>
@@ -1816,67 +1819,55 @@
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
       <c r="I8" s="7"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="6" t="n">
-        <v>13</v>
-      </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="7"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="F10" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="7"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -1884,211 +1875,221 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
       <c r="I12" s="7"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="C13" s="6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>16</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>27</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H13" s="6"/>
       <c r="I13" s="7"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I14" s="7"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I15" s="7"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -2101,7 +2102,7 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2116,167 +2117,167 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>19</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I22" s="7"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>19</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I23" s="7"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I24" s="7"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="C25" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="7"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I26" s="7"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>21</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -2289,61 +2290,61 @@
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>22</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="D30" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>23</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I30" s="7"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2358,88 +2359,88 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="D32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>25</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I32" s="7"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="D33" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>25</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I33" s="7"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="D34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I34" s="7"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -2452,7 +2453,7 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2467,7 +2468,7 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2482,7 +2483,7 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2497,572 +2498,584 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="D39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I39" s="7"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="D40" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I40" s="7"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I48" s="7"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
+        <v>78</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="I49" s="7"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
-      <c r="F50" s="6" t="n">
-        <v>31</v>
-      </c>
+      <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="7"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>103</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
       <c r="F51" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>32</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
       <c r="I51" s="7"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I52" s="7"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="C53" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I53" s="7"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
+        <v>103</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>106</v>
+      </c>
       <c r="F54" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I54" s="7"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>113</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
       <c r="F55" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
       <c r="I55" s="7"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
+        <v>109</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I56" s="7"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
       <c r="I57" s="7"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
+        <v>114</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="F58" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I58" s="7"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>122</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
       <c r="F59" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
       <c r="I59" s="7"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D60" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F60" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>39</v>
-      </c>
       <c r="G60" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I60" s="7"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+        <v>122</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I61" s="7"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
-      <c r="F62" s="6" t="n">
-        <v>40</v>
-      </c>
+      <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
       <c r="I62" s="7"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
@@ -3070,399 +3083,413 @@
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>121</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
       <c r="F64" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>32</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
       <c r="I64" s="7"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I65" s="7"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="C66" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="I66" s="7"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C67" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="I67" s="7"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C68" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C69" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I69" s="7"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C70" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I70" s="7"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
+        <v>132</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="I71" s="7"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>45</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
       <c r="I72" s="7"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B75" s="6" t="s">
-        <v>157</v>
-      </c>
       <c r="C75" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
+        <v>153</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="F76" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I76" s="7"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="D78" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
+      <c r="C79" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>165</v>
+      </c>
       <c r="I79" s="7"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>166</v>
@@ -3471,19 +3498,19 @@
         <v>167</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I80" s="7"/>
     </row>
@@ -3491,109 +3518,121 @@
       <c r="A81" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B81" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
       <c r="I81" s="7"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I82" s="7"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
+        <v>172</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="F83" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I83" s="7"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
+      <c r="B84" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="F84" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I84" s="7"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
+      <c r="F85" s="6" t="n">
+        <v>51</v>
+      </c>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
       <c r="I85" s="7"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
@@ -3601,29 +3640,27 @@
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
-      <c r="F87" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
       <c r="I87" s="7"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
@@ -3631,383 +3668,413 @@
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C89" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D89" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>180</v>
-      </c>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
       <c r="F89" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>27</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
       <c r="I89" s="7"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" s="6" t="s">
         <v>180</v>
       </c>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
       <c r="F90" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>27</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
       <c r="I90" s="7"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>182</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I91" s="7"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="D92" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E92" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I92" s="7"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>186</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I93" s="7"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>187</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I94" s="7"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
+        <v>181</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I95" s="7"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
+        <v>181</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>184</v>
+      </c>
       <c r="F96" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="I96" s="7"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C97" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D97" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
       <c r="I97" s="7"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>197</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
       <c r="F98" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>53</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
       <c r="I98" s="7"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
+        <v>194</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>197</v>
+      </c>
       <c r="F99" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I99" s="7"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
+      <c r="C100" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I100" s="7"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C101" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D101" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>203</v>
-      </c>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
       <c r="F101" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
       <c r="I101" s="7"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
-      <c r="F102" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="7"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
+      <c r="C103" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="F103" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I103" s="7"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E104" s="6" t="s">
         <v>208</v>
       </c>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
       <c r="F104" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F106" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G104" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I104" s="7"/>
+      <c r="G106" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I106" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:G6"/>
-  <conditionalFormatting sqref="A7:H105">
+  <conditionalFormatting sqref="A7:H107">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>=AND($A7&lt;&gt;$A6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I104">
+  <conditionalFormatting sqref="A7:I106">
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>=LEFT($A7, 3)="MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:H104">
+  <conditionalFormatting sqref="A7:H106">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>=LEFT($A7,3)&lt;&gt;"MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B104">
+  <conditionalFormatting sqref="B7:B106">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>=AND($B7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A104">
+  <conditionalFormatting sqref="A7:A106">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=0,$E7=$E6)</formula>
     </cfRule>
@@ -4015,7 +4082,7 @@
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=1,$E7=$E6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D104">
+  <conditionalFormatting sqref="D7:D106">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>=AND($D7="confirmed")</formula>
     </cfRule>
@@ -4053,17 +4120,16 @@
     <col min="12" max="12" width="30.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="30.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="30.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="30.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -4078,1905 +4144,1836 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>39</v>
+        <v>217</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>223</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="L7" s="12" t="s">
         <v>228</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>229</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O7" s="13"/>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O8" s="13"/>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O9" s="13"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O10" s="13"/>
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O11" s="13"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O12" s="13"/>
       <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O13" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O13" s="13"/>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O14" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O14" s="13"/>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O15" s="13"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O16" s="13"/>
       <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>256</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O17" s="13"/>
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O18" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O18" s="13"/>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O19" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O20" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O21" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O21" s="13"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>266</v>
+        <v>228</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O22" s="13"/>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O23" s="13"/>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>225</v>
+        <v>273</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O24" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O24" s="13"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>266</v>
+        <v>228</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O26" s="13"/>
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>280</v>
+        <v>228</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>225</v>
+        <v>283</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O27" s="13"/>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O28" s="13"/>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O29" s="13"/>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O30" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O30" s="13"/>
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>225</v>
+        <v>288</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O31" s="13"/>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O32" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O32" s="13"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="B33" s="11"/>
       <c r="C33" s="12" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O33" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O33" s="13"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
-      <c r="R33" s="13"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
         <v>291</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O34" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O34" s="13"/>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="J35" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>287</v>
-      </c>
       <c r="K35" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O35" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O35" s="13"/>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
         <v>294</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>295</v>
+        <v>23</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>225</v>
+        <v>288</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O36" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O36" s="13"/>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C37" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>297</v>
+        <v>228</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O37" s="13"/>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
-      <c r="R37" s="13"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="L38" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="B38" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>225</v>
-      </c>
       <c r="M38" s="12" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O38" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O38" s="13"/>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
-      <c r="R38" s="13"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
         <v>299</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>225</v>
+        <v>288</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O39" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O39" s="13"/>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
-      <c r="R39" s="13"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
         <v>300</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>301</v>
+        <v>228</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>302</v>
+        <v>228</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>303</v>
+        <v>228</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O40" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O40" s="13"/>
       <c r="P40" s="13"/>
       <c r="Q40" s="13"/>
-      <c r="R40" s="13"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="K41" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>306</v>
-      </c>
       <c r="L41" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O41" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O41" s="13"/>
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
-      <c r="R41" s="13"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="J42" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="B42" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>225</v>
-      </c>
       <c r="K42" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O42" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O42" s="13"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
-      <c r="R42" s="13"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
         <v>308</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O43" s="12" t="s">
-        <v>225</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O43" s="13"/>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
-      <c r="R43" s="13"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="O44" s="13"/>
+      <c r="P44" s="13"/>
+      <c r="Q44" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:O6"/>
-  <conditionalFormatting sqref="C7:O43">
+  <autoFilter ref="A6:N6"/>
+  <conditionalFormatting sqref="C7:N44">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>ISNUMBER(SEARCH("confirmed", INDIRECT("RC", FALSE)))</formula>
     </cfRule>
@@ -6012,12 +6009,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -6030,319 +6027,319 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/civil-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C7" s="11" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/community-performance-annual-update-to-march-2025", "Link to publication")</f>
       </c>
       <c r="C8" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/coroners-and-burials-statistics", "Link to publication")</f>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-court-statistics", "Link to publication")</f>
       </c>
       <c r="C10" s="11" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>329</v>
-      </c>
       <c r="G10" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C11" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/death-of-offenders-in-the-community", "Link to publication")</f>
       </c>
       <c r="C12" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>334</v>
-      </c>
       <c r="G12" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/diversity-of-the-judiciary-2024-statistics", "Link to publication")</f>
       </c>
       <c r="C13" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>337</v>
-      </c>
       <c r="G13" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/electronic-monitoring-statistics-annual-publication-march-2024", "Link to publication")</f>
       </c>
       <c r="C14" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>340</v>
-      </c>
       <c r="G14" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B15" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/electronic-monitoring-publication", "Link to publication")</f>
       </c>
       <c r="C15" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E15" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>340</v>
-      </c>
       <c r="G15" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B16" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/ethnicity-and-the-criminal-justice-system-2024", "Link to publication")</f>
       </c>
       <c r="C16" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B17" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/family-court-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C17" s="11" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6356,358 +6353,358 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B19" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C19" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B20" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C20" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B21" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-offender-equalities-report", "Link to publication")</f>
       </c>
       <c r="C21" s="11" t="s">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>352</v>
-      </c>
       <c r="G21" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C22" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-staff-equalities-report", "Link to publication")</f>
       </c>
       <c r="C23" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/justice-data-lab", "Link to publication")</f>
       </c>
       <c r="C24" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/knife-and-offensive-weapon-sentencing-statistics", "Link to publication")</f>
       </c>
       <c r="C25" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/legal-aid-statistics", "Link to publication")</f>
       </c>
       <c r="C26" s="11" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B27" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/mortgage-and-landlord-possession-statistics", "Link to publication")</f>
       </c>
       <c r="C27" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/multi-agency-public-protection-arrangements-mappa-annual-reports", "Link to publication")</f>
       </c>
       <c r="C28" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B29" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-accommodation-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C29" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B30" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-employment-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C30" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B31" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-management-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C31" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B32" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
       </c>
       <c r="C32" s="11" t="s">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="D32" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H32" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -6715,77 +6712,65 @@
         <v>290</v>
       </c>
       <c r="B33" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>376</v>
-      </c>
+        <f>HYPERLINK("NA", "Link to publication")</f>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
         <v>291</v>
       </c>
       <c r="B34" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C34" s="11" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="D34" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H34" s="11" t="s">
         <v>377</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B35" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
       </c>
       <c r="C35" s="11" t="s">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="D35" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H35" s="11" t="s">
         <v>380</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -6793,18 +6778,22 @@
         <v>294</v>
       </c>
       <c r="B36" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C36" s="11" t="s">
-        <v>295</v>
+        <v>23</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
+        <v>381</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>381</v>
+      </c>
       <c r="G36" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>382</v>
@@ -6812,54 +6801,50 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B37" s="17" t="str">
+        <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B37" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="D37" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H37" s="11" t="s">
         <v>383</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B38" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
       </c>
       <c r="C38" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>386</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -6867,18 +6852,22 @@
         <v>299</v>
       </c>
       <c r="B39" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
       </c>
       <c r="C39" s="11" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
+        <v>387</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>387</v>
+      </c>
       <c r="G39" s="11" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>389</v>
@@ -6889,77 +6878,73 @@
         <v>300</v>
       </c>
       <c r="B40" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C40" s="11" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="D40" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H40" s="11" t="s">
         <v>390</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B41" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
       </c>
       <c r="C41" s="11" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>368</v>
+        <v>321</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>391</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B42" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
       </c>
       <c r="C42" s="11" t="s">
-        <v>252</v>
+        <v>41</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -6967,25 +6952,51 @@
         <v>308</v>
       </c>
       <c r="B43" s="17" t="str">
+        <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B44" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
       </c>
-      <c r="C43" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="E43" s="11" t="s">
+      <c r="C44" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="G43" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="H43" s="11" t="s">
+      <c r="F44" s="11" t="s">
         <v>395</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="399">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Weekly View)</t>
   </si>
@@ -223,21 +223,15 @@
     <t xml:space="preserve">Thu 28 May 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Criminal court statistics quarterly: January to March 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Family court statistics quarterly: January to March 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Mon 29 Jun 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Criminal court statistics quarterly: January to March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tue 30 Jun 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tue 02 Jun 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">July 2026</t>
   </si>
   <si>
@@ -655,6 +649,18 @@
     <t xml:space="preserve">Thu 25 Feb 2027</t>
   </si>
   <si>
+    <t xml:space="preserve">Mon 29 Mar 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criminal court statistics quarterly: October to December 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tue 30 Mar 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tue 02 Mar 2027</t>
+  </si>
+  <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Monthly Grid)</t>
   </si>
   <si>
@@ -730,7 +736,7 @@
     <t xml:space="preserve">Criminal court statistics quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Tue 30 Jun 2026 (provisional)</t>
+    <t xml:space="preserve">Thu 25 Jun 2026 (confirmed)</t>
   </si>
   <si>
     <t xml:space="preserve">Wed 30 Sep 2026 (provisional)</t>
@@ -739,6 +745,9 @@
     <t xml:space="preserve">Thu 17 Dec 2026 (provisional)</t>
   </si>
   <si>
+    <t xml:space="preserve">Tue 30 Mar 2027 (provisional)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Criminal Justice statistics quarterly</t>
   </si>
   <si>
@@ -848,9 +857,6 @@
   </si>
   <si>
     <t xml:space="preserve">Legal aid statistics quarterly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 25 Jun 2026 (confirmed)</t>
   </si>
   <si>
     <t xml:space="preserve">Mortgage and landlord possession statistics</t>
@@ -2395,7 +2401,7 @@
         <v>67</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>68</v>
@@ -2413,22 +2419,22 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="C34" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>22</v>
@@ -2440,42 +2446,42 @@
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
+      <c r="F35" s="6" t="n">
+        <v>26</v>
+      </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="7"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
-      <c r="F36" s="6" t="n">
-        <v>27</v>
-      </c>
+      <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="7"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -2483,14 +2489,14 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -2498,46 +2504,34 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>81</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
       <c r="F39" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
       <c r="I39" s="7"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>30</v>
@@ -2546,25 +2540,25 @@
         <v>22</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="I40" s="7"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>30</v>
@@ -2573,25 +2567,25 @@
         <v>22</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>30</v>
@@ -2606,19 +2600,19 @@
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>30</v>
@@ -2633,19 +2627,19 @@
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>30</v>
@@ -2654,25 +2648,25 @@
         <v>22</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>20</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>30</v>
@@ -2681,25 +2675,25 @@
         <v>22</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>20</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>30</v>
@@ -2708,25 +2702,25 @@
         <v>22</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>30</v>
@@ -2735,25 +2729,25 @@
         <v>22</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>30</v>
@@ -2762,25 +2756,25 @@
         <v>22</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I48" s="7"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>30</v>
@@ -2789,83 +2783,83 @@
         <v>22</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="I49" s="7"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="I50" s="7"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
-      <c r="F51" s="6" t="n">
-        <v>31</v>
-      </c>
+      <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="7"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
       <c r="F52" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
       <c r="I52" s="7"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>22</v>
@@ -2877,19 +2871,19 @@
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>33</v>
@@ -2898,152 +2892,152 @@
         <v>22</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="I54" s="7"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="F55" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I55" s="7"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>112</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
       <c r="F56" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
       <c r="I56" s="7"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I57" s="7"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
       <c r="I58" s="7"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
+        <v>112</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="F59" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I59" s="7"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>121</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
       <c r="F60" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
       <c r="I60" s="7"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>22</v>
@@ -3055,42 +3049,54 @@
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I62" s="7"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
-      <c r="F63" s="6" t="n">
-        <v>40</v>
-      </c>
+      <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
       <c r="I63" s="7"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
@@ -3098,73 +3104,61 @@
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>120</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
       <c r="F65" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
       <c r="I65" s="7"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I66" s="7"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="D67" s="6" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>43</v>
@@ -3173,25 +3167,25 @@
         <v>22</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="I67" s="7"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>43</v>
@@ -3200,25 +3194,25 @@
         <v>22</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>43</v>
@@ -3233,19 +3227,19 @@
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>43</v>
@@ -3260,19 +3254,19 @@
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>43</v>
@@ -3287,113 +3281,113 @@
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
+        <v>130</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="I72" s="7"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>41</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
       <c r="I73" s="7"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>46</v>
@@ -3402,52 +3396,52 @@
         <v>22</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="I76" s="7"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>47</v>
@@ -3456,52 +3450,52 @@
         <v>22</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I79" s="7"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>48</v>
@@ -3510,68 +3504,68 @@
         <v>22</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>60</v>
+        <v>163</v>
       </c>
       <c r="I80" s="7"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
+        <v>161</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I81" s="7"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
       <c r="I82" s="7"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G83" s="6" t="s">
         <v>22</v>
@@ -3583,19 +3577,19 @@
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>50</v>
@@ -3610,29 +3604,41 @@
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
+        <v>170</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>153</v>
+      </c>
       <c r="F85" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I85" s="7"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
@@ -3640,42 +3646,42 @@
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
+      <c r="F87" s="6" t="n">
+        <v>52</v>
+      </c>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
       <c r="I87" s="7"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
-      <c r="F88" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
       <c r="I88" s="7"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
       <c r="F89" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
@@ -3683,14 +3689,14 @@
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
       <c r="F90" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
@@ -3698,46 +3704,34 @@
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>184</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
       <c r="F91" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
       <c r="I91" s="7"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>4</v>
@@ -3752,19 +3746,19 @@
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B93" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="D93" s="6" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>4</v>
@@ -3779,19 +3773,19 @@
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D94" s="6" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>4</v>
@@ -3806,19 +3800,19 @@
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>4</v>
@@ -3827,25 +3821,25 @@
         <v>22</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I95" s="7"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>4</v>
@@ -3854,172 +3848,184 @@
         <v>22</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I96" s="7"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
+        <v>179</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="I97" s="7"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
-      <c r="F98" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
       <c r="I98" s="7"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>197</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
       <c r="F99" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
       <c r="I99" s="7"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G100" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="I100" s="7"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
+        <v>196</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>199</v>
+      </c>
       <c r="F101" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I101" s="7"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
+      <c r="F102" s="6" t="n">
+        <v>8</v>
+      </c>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="7"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="F103" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
       <c r="I103" s="7"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
+        <v>202</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>205</v>
+      </c>
       <c r="F104" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="I104" s="7"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
       <c r="F105" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
@@ -4027,54 +4033,96 @@
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E107" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B106" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C106" s="6" t="s">
+      <c r="F107" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="B108" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D108" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E106" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F106" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G106" s="6" t="s">
+      <c r="E108" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G108" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H106" s="6" t="s">
+      <c r="H108" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I106" s="7"/>
+      <c r="I108" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:G6"/>
-  <conditionalFormatting sqref="A7:H107">
+  <conditionalFormatting sqref="A7:H109">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>=AND($A7&lt;&gt;$A6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I106">
+  <conditionalFormatting sqref="A7:I108">
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>=LEFT($A7, 3)="MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:H106">
+  <conditionalFormatting sqref="A7:H108">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>=LEFT($A7,3)&lt;&gt;"MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B106">
+  <conditionalFormatting sqref="B7:B108">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>=AND($B7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A106">
+  <conditionalFormatting sqref="A7:A108">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=0,$E7=$E6)</formula>
     </cfRule>
@@ -4082,7 +4130,7 @@
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=1,$E7=$E6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D106">
+  <conditionalFormatting sqref="D7:D108">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>=AND($D7="confirmed")</formula>
     </cfRule>
@@ -4124,12 +4172,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -4144,46 +4192,46 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
@@ -4191,46 +4239,46 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
@@ -4238,46 +4286,46 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
@@ -4285,46 +4333,46 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
@@ -4332,46 +4380,46 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
@@ -4379,46 +4427,46 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
@@ -4426,46 +4474,46 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
@@ -4473,46 +4521,46 @@
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
@@ -4520,46 +4568,46 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O14" s="13"/>
       <c r="P14" s="13"/>
@@ -4567,46 +4615,46 @@
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O15" s="13"/>
       <c r="P15" s="13"/>
@@ -4614,46 +4662,46 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
@@ -4661,46 +4709,46 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O17" s="13"/>
       <c r="P17" s="13"/>
@@ -4708,44 +4756,44 @@
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
@@ -4753,46 +4801,46 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
@@ -4800,46 +4848,46 @@
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
@@ -4847,46 +4895,46 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
@@ -4894,46 +4942,46 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
@@ -4941,46 +4989,46 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
@@ -4988,46 +5036,46 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
@@ -5035,46 +5083,46 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
@@ -5082,46 +5130,46 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
@@ -5129,46 +5177,46 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
@@ -5176,46 +5224,46 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O28" s="13"/>
       <c r="P28" s="13"/>
@@ -5223,46 +5271,46 @@
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
@@ -5270,46 +5318,46 @@
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O30" s="13"/>
       <c r="P30" s="13"/>
@@ -5317,46 +5365,46 @@
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
@@ -5364,46 +5412,46 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
@@ -5411,44 +5459,44 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
@@ -5456,46 +5504,46 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O34" s="13"/>
       <c r="P34" s="13"/>
@@ -5503,46 +5551,46 @@
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O35" s="13"/>
       <c r="P35" s="13"/>
@@ -5550,46 +5598,46 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O36" s="13"/>
       <c r="P36" s="13"/>
@@ -5597,46 +5645,46 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
@@ -5644,46 +5692,46 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
@@ -5691,46 +5739,46 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
@@ -5738,46 +5786,46 @@
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O40" s="13"/>
       <c r="P40" s="13"/>
@@ -5785,46 +5833,46 @@
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O41" s="13"/>
       <c r="P41" s="13"/>
@@ -5832,46 +5880,46 @@
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>41</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
@@ -5879,46 +5927,46 @@
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O43" s="13"/>
       <c r="P43" s="13"/>
@@ -5926,46 +5974,46 @@
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O44" s="13"/>
       <c r="P44" s="13"/>
@@ -6009,12 +6057,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -6027,33 +6075,33 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/civil-justice-statistics-quarterly", "Link to publication")</f>
@@ -6062,50 +6110,50 @@
         <v>60</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/community-performance-annual-update-to-march-2025", "Link to publication")</f>
       </c>
       <c r="C8" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D8" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>322</v>
-      </c>
       <c r="H8" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/coroners-and-burials-statistics", "Link to publication")</f>
@@ -6114,24 +6162,24 @@
         <v>44</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-court-statistics", "Link to publication")</f>
@@ -6140,24 +6188,24 @@
         <v>60</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
@@ -6166,102 +6214,102 @@
         <v>29</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>331</v>
-      </c>
       <c r="F11" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/death-of-offenders-in-the-community", "Link to publication")</f>
       </c>
       <c r="C12" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/diversity-of-the-judiciary-2024-statistics", "Link to publication")</f>
       </c>
       <c r="C13" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/electronic-monitoring-statistics-annual-publication-march-2024", "Link to publication")</f>
       </c>
       <c r="C14" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B15" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/electronic-monitoring-publication", "Link to publication")</f>
@@ -6270,50 +6318,50 @@
         <v>23</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B16" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/ethnicity-and-the-criminal-justice-system-2024", "Link to publication")</f>
       </c>
       <c r="C16" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>331</v>
-      </c>
       <c r="F16" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B17" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/family-court-statistics-quarterly", "Link to publication")</f>
@@ -6322,24 +6370,24 @@
         <v>60</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6353,85 +6401,85 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B19" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C19" s="11" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B20" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C20" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B21" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-offender-equalities-report", "Link to publication")</f>
       </c>
       <c r="C21" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
@@ -6440,46 +6488,46 @@
         <v>29</v>
       </c>
       <c r="D22" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>354</v>
-      </c>
       <c r="F22" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-staff-equalities-report", "Link to publication")</f>
       </c>
       <c r="C23" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D23" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>354</v>
-      </c>
       <c r="F23" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/justice-data-lab", "Link to publication")</f>
@@ -6488,24 +6536,24 @@
         <v>23</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B25" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/knife-and-offensive-weapon-sentencing-statistics", "Link to publication")</f>
@@ -6514,24 +6562,24 @@
         <v>50</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B26" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/legal-aid-statistics", "Link to publication")</f>
@@ -6540,24 +6588,24 @@
         <v>60</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/mortgage-and-landlord-possession-statistics", "Link to publication")</f>
@@ -6566,98 +6614,98 @@
         <v>29</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B28" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/multi-agency-public-protection-arrangements-mappa-annual-reports", "Link to publication")</f>
       </c>
       <c r="C28" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B29" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-accommodation-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C29" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B30" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-employment-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C30" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B31" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-management-statistics-quarterly", "Link to publication")</f>
@@ -6666,50 +6714,50 @@
         <v>23</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B32" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
       </c>
       <c r="C32" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E32" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="H32" s="11" t="s">
         <v>354</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B33" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6723,59 +6771,59 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C34" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B35" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
       </c>
       <c r="C35" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B36" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
@@ -6784,46 +6832,46 @@
         <v>23</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B37" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
       </c>
       <c r="C37" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B38" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
@@ -6832,24 +6880,24 @@
         <v>23</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B39" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
@@ -6858,46 +6906,46 @@
         <v>23</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B40" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C40" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B41" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
@@ -6906,24 +6954,24 @@
         <v>60</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B42" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
@@ -6932,71 +6980,71 @@
         <v>41</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B43" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
       </c>
       <c r="C43" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D43" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="E43" s="11" t="s">
-        <v>331</v>
-      </c>
       <c r="F43" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B44" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
       </c>
       <c r="C44" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="394">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Weekly View)</t>
   </si>
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Last updated:  Thursday 02 April 2026</t>
+    <t xml:space="preserve">Last updated:  Monday 20 April 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Week Commencing</t>
@@ -52,21 +52,9 @@
     <t xml:space="preserve">Usual publication month(s)</t>
   </si>
   <si>
-    <t xml:space="preserve">March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 30 Mar 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 06 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 13 Apr 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mon 20 Apr 2026</t>
   </si>
   <si>
@@ -160,6 +148,9 @@
     <t xml:space="preserve">Thu 21 May 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Mortgage and landlord possession statistics: January to March 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">First time entrants (FTE) and Offender Histories: 2025</t>
   </si>
   <si>
@@ -172,15 +163,6 @@
     <t xml:space="preserve">Mon 25 May 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Mortgage and landlord possession statistics: January to March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun 31 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun 03 May 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">June 2026</t>
   </si>
   <si>
@@ -238,6 +220,15 @@
     <t xml:space="preserve">Mon 06 Jul 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Diversity of the judiciary: 2026 statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 09 Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">July </t>
+  </si>
+  <si>
     <t xml:space="preserve">Mon 13 Jul 2026</t>
   </si>
   <si>
@@ -772,7 +763,7 @@
     <t xml:space="preserve">Diversity of the judiciary</t>
   </si>
   <si>
-    <t xml:space="preserve">July </t>
+    <t xml:space="preserve">Thu 09 Jul 2026 (provisional)</t>
   </si>
   <si>
     <t xml:space="preserve">Electronic Monitoring Statistics Annual Publication</t>
@@ -805,7 +796,7 @@
     <t xml:space="preserve">first time entrants (fte) and offender histories</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 21 May 2026 (provisional)</t>
+    <t xml:space="preserve">Thu 21 May 2026 (confirmed)</t>
   </si>
   <si>
     <t xml:space="preserve">First time entrants (FTE) into the Criminal Justice System and Offender Histories</t>
@@ -826,9 +817,6 @@
     <t xml:space="preserve">HMPPS workforce quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 21 May 2026 (confirmed)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thu 20 Aug 2026 (provisional)</t>
   </si>
   <si>
@@ -860,9 +848,6 @@
   </si>
   <si>
     <t xml:space="preserve">Mortgage and landlord possession statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun 31 May 2026 (provisional)</t>
   </si>
   <si>
     <t xml:space="preserve">Thu 13 Aug 2026 (provisional)</t>
@@ -1825,622 +1810,634 @@
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="F8" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I8" s="7"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="F10" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I10" s="7"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="F11" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I11" s="7"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="I12" s="7"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="G13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6"/>
       <c r="I13" s="7"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I14" s="7"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I15" s="7"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
       <c r="I16" s="7"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>28</v>
-      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
       <c r="I17" s="7"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+      <c r="H21" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>19</v>
-      </c>
       <c r="G22" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>41</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="7"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I23" s="7"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
       <c r="F24" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
       <c r="I24" s="7"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>22</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="7"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I26" s="7"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="F28" s="6" t="n">
+        <v>24</v>
+      </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="7"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="D30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="F30" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I30" s="7"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
+      <c r="C31" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="F31" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="I31" s="7"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>68</v>
-      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
       <c r="F32" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
       <c r="I32" s="7"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
       <c r="I33" s="7"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="I34" s="7"/>
     </row>
@@ -2453,7 +2450,7 @@
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -2467,7 +2464,9 @@
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
+      <c r="F36" s="6" t="n">
+        <v>29</v>
+      </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="7"/>
@@ -2476,645 +2475,681 @@
       <c r="A37" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
+      <c r="B37" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="F37" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="F38" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="F39" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I39" s="7"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I40" s="7"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="D41" s="6" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B48" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
       <c r="I48" s="7"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>84</v>
-      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
       <c r="F49" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
       <c r="I49" s="7"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="I50" s="7"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I51" s="7"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="F52" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I52" s="7"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
       <c r="F53" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
       <c r="I53" s="7"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="I54" s="7"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>50</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
       <c r="I55" s="7"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
+        <v>109</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="F56" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="I56" s="7"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>110</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
       <c r="F57" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
       <c r="I57" s="7"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
+        <v>113</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="I58" s="7"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I59" s="7"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
-      <c r="F60" s="6" t="n">
-        <v>37</v>
-      </c>
+      <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
       <c r="I60" s="7"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>119</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
       <c r="F61" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
       <c r="I61" s="7"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E62" s="6" t="s">
         <v>123</v>
       </c>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
       <c r="F62" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
       <c r="I62" s="7"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
+      <c r="B63" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I63" s="7"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
+        <v>127</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="F64" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I64" s="7"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
+        <v>127</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="F65" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="I65" s="7"/>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -3122,40 +3157,40 @@
         <v>127</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D66" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F66" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>42</v>
-      </c>
       <c r="G66" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I66" s="7"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>132</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>133</v>
@@ -3164,469 +3199,431 @@
         <v>43</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I67" s="7"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>138</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I69" s="7"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B70" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
       <c r="I70" s="7"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I71" s="7"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I72" s="7"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
+        <v>148</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="I76" s="7"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>160</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
       <c r="I79" s="7"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="I80" s="7"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I81" s="7"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
+        <v>167</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="I82" s="7"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>149</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
       <c r="F83" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
       <c r="I83" s="7"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B84" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>153</v>
-      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
       <c r="F84" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
       <c r="I84" s="7"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C85" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
       <c r="I85" s="7"/>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3638,7 +3635,7 @@
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
@@ -3653,7 +3650,7 @@
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
@@ -3667,7 +3664,9 @@
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
+      <c r="F88" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
       <c r="I88" s="7"/>
@@ -3676,232 +3675,256 @@
       <c r="A89" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
+      <c r="B89" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>179</v>
+      </c>
       <c r="F89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I89" s="7"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
+        <v>176</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>179</v>
+      </c>
       <c r="F90" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I90" s="7"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
+      <c r="D91" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>179</v>
+      </c>
       <c r="F91" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I91" s="7"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I92" s="7"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E93" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I93" s="7"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I94" s="7"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E95" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F95" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
       <c r="I95" s="7"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B96" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>182</v>
-      </c>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
       <c r="F96" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
       <c r="I96" s="7"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I97" s="7"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
+        <v>193</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I98" s="7"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
       <c r="F99" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
@@ -3909,68 +3932,54 @@
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
       <c r="I100" s="7"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I101" s="7"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
@@ -3978,151 +3987,96 @@
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
+      <c r="F103" s="6" t="n">
+        <v>11</v>
+      </c>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
       <c r="I103" s="7"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I104" s="7"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
+        <v>208</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="F105" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="I105" s="7"/>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="7"/>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F107" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I107" s="7"/>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="F108" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I108" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:G6"/>
-  <conditionalFormatting sqref="A7:H109">
+  <conditionalFormatting sqref="A7:H106">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>=AND($A7&lt;&gt;$A6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I108">
+  <conditionalFormatting sqref="A7:I105">
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>=LEFT($A7, 3)="MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:H108">
+  <conditionalFormatting sqref="A7:H105">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>=LEFT($A7,3)&lt;&gt;"MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B108">
+  <conditionalFormatting sqref="B7:B105">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>=AND($B7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A108">
+  <conditionalFormatting sqref="A7:A105">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=0,$E7=$E6)</formula>
     </cfRule>
@@ -4130,7 +4084,7 @@
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=1,$E7=$E6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D108">
+  <conditionalFormatting sqref="D7:D105">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>=AND($D7="confirmed")</formula>
     </cfRule>
@@ -4172,12 +4126,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -4192,46 +4146,46 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>228</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
@@ -4239,46 +4193,46 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H7" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="I7" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="K7" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E7" s="12" t="s">
+      <c r="L7" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="N7" s="12" t="s">
         <v>231</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>234</v>
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
@@ -4286,46 +4240,46 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
@@ -4333,46 +4287,46 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
@@ -4380,46 +4334,46 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="K10" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="L10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="N10" s="12" t="s">
         <v>240</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>243</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
@@ -4427,46 +4381,46 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="J11" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L11" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>248</v>
-      </c>
       <c r="M11" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
@@ -4474,46 +4428,46 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
@@ -4521,46 +4475,46 @@
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>252</v>
+        <v>70</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
@@ -4568,46 +4522,46 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O14" s="13"/>
       <c r="P14" s="13"/>
@@ -4615,46 +4569,46 @@
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O15" s="13"/>
       <c r="P15" s="13"/>
@@ -4662,46 +4616,46 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
@@ -4709,46 +4663,46 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="N17" s="12" t="s">
         <v>258</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>261</v>
       </c>
       <c r="O17" s="13"/>
       <c r="P17" s="13"/>
@@ -4756,44 +4710,44 @@
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
@@ -4801,46 +4755,46 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
@@ -4848,46 +4802,46 @@
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
@@ -4895,46 +4849,46 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
@@ -4942,46 +4896,46 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
@@ -4989,46 +4943,46 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
@@ -5036,46 +4990,46 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
@@ -5083,46 +5037,46 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
@@ -5130,46 +5084,46 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
@@ -5177,46 +5131,46 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
@@ -5224,46 +5178,46 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O28" s="13"/>
       <c r="P28" s="13"/>
@@ -5271,46 +5225,46 @@
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
@@ -5318,46 +5272,46 @@
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O30" s="13"/>
       <c r="P30" s="13"/>
@@ -5365,46 +5319,46 @@
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C31" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L31" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>248</v>
-      </c>
       <c r="M31" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
@@ -5412,46 +5366,46 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
@@ -5459,44 +5413,44 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
@@ -5504,46 +5458,46 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O34" s="13"/>
       <c r="P34" s="13"/>
@@ -5551,46 +5505,46 @@
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O35" s="13"/>
       <c r="P35" s="13"/>
@@ -5598,46 +5552,46 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C36" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L36" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="K36" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>248</v>
-      </c>
       <c r="M36" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O36" s="13"/>
       <c r="P36" s="13"/>
@@ -5645,46 +5599,46 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
@@ -5692,46 +5646,46 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
@@ -5739,46 +5693,46 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L39" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D39" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="L39" s="12" t="s">
-        <v>248</v>
-      </c>
       <c r="M39" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
@@ -5786,46 +5740,46 @@
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O40" s="13"/>
       <c r="P40" s="13"/>
@@ -5833,46 +5787,46 @@
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O41" s="13"/>
       <c r="P41" s="13"/>
@@ -5880,46 +5834,46 @@
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
@@ -5927,46 +5881,46 @@
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O43" s="13"/>
       <c r="P43" s="13"/>
@@ -5974,46 +5928,46 @@
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O44" s="13"/>
       <c r="P44" s="13"/>
@@ -6057,12 +6011,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -6075,319 +6029,319 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/civil-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C7" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/community-performance-annual-update-to-march-2025", "Link to publication")</f>
       </c>
       <c r="C8" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G8" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>324</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/coroners-and-burials-statistics", "Link to publication")</f>
       </c>
       <c r="C9" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-court-statistics", "Link to publication")</f>
       </c>
       <c r="C10" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C11" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/death-of-offenders-in-the-community", "Link to publication")</f>
       </c>
       <c r="C12" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/diversity-of-the-judiciary-2024-statistics", "Link to publication")</f>
       </c>
       <c r="C13" s="11" t="s">
-        <v>252</v>
+        <v>70</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/electronic-monitoring-statistics-annual-publication-march-2024", "Link to publication")</f>
       </c>
       <c r="C14" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B15" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/electronic-monitoring-publication", "Link to publication")</f>
       </c>
       <c r="C15" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B16" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/ethnicity-and-the-criminal-justice-system-2024", "Link to publication")</f>
       </c>
       <c r="C16" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B17" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/family-court-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C17" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6401,363 +6355,363 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B19" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C19" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B20" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C20" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B21" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-offender-equalities-report", "Link to publication")</f>
       </c>
       <c r="C21" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C22" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-staff-equalities-report", "Link to publication")</f>
       </c>
       <c r="C23" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/justice-data-lab", "Link to publication")</f>
       </c>
       <c r="C24" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B25" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/knife-and-offensive-weapon-sentencing-statistics", "Link to publication")</f>
       </c>
       <c r="C25" s="11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B26" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/legal-aid-statistics", "Link to publication")</f>
       </c>
       <c r="C26" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B27" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/mortgage-and-landlord-possession-statistics", "Link to publication")</f>
       </c>
       <c r="C27" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B28" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/multi-agency-public-protection-arrangements-mappa-annual-reports", "Link to publication")</f>
       </c>
       <c r="C28" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B29" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-accommodation-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C29" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B30" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-employment-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C30" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B31" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-management-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C31" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B32" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
       </c>
       <c r="C32" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B33" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6771,280 +6725,280 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B34" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C34" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B35" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
       </c>
       <c r="C35" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B36" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C36" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B37" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
       </c>
       <c r="C37" s="11" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B38" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
       </c>
       <c r="C38" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B39" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
       </c>
       <c r="C39" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B40" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C40" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B41" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
       </c>
       <c r="C41" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B42" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
       </c>
       <c r="C42" s="11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B43" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
       </c>
       <c r="C43" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B44" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
       </c>
       <c r="C44" s="11" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t xml:space="preserve">MoJ Statistics Forward Look (Weekly View)</t>
   </si>
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Last updated:  Monday 20 April 2026</t>
+    <t xml:space="preserve">Last updated:  Monday 27 April 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Week Commencing</t>
@@ -55,126 +55,114 @@
     <t xml:space="preserve">April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Mon 20 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronic Monitoring Statistics Publication, March 2026</t>
+    <t xml:space="preserve">Mon 27 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criminal Justice Statistics Quarterly: December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 30 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 02 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb, May, Aug,Nov </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety in the Children and Young People Secure Estate: Update to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan, Apr, Jul, Oct </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety in custody: quarterly update to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offender management statistics quarterly: October to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proven reoffending statistics: April to June 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justice data lab statistics: April 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 04 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 11 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unpaid work management information, update to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 14 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 16 Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May, Nov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coroners statistics 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 18 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HM Prison &amp; Probation Service workforce quarterly: March 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 21 May 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Thu 23 Apr 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 26 Mar 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan, Apr, Jul, Oct </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prison leavers in substance misuse treatment: 4-week outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 27 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criminal Justice Statistics Quarterly: December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 30 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 02 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb, May, Aug,Nov </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safety in the Children and Young People Secure Estate: Update to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safety in custody: quarterly update to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offender management statistics quarterly: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proven reoffending statistics: April to June 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justice data lab statistics: April 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 04 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 11 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unpaid work management information, update to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 14 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 16 Apr 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May, Nov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coroners statistics 2025</t>
+    <t xml:space="preserve">Mortgage and landlord possession statistics: January to March 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First time entrants (FTE) and Offender Histories: 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knife and Offensive Weapon Sentencing Statistics: October to December 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb, May, Aug, Nov </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 25 May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">June 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon 01 Jun 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil justice statistics quarterly: January to March 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu 04 Jun 2026</t>
   </si>
   <si>
     <t xml:space="preserve">provisional</t>
   </si>
   <si>
-    <t xml:space="preserve">May </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 18 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HM Prison &amp; Probation Service workforce quarterly: March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 21 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortgage and landlord possession statistics: January to March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First time entrants (FTE) and Offender Histories: 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knife and Offensive Weapon Sentencing Statistics: October to December 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb, May, Aug, Nov </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 25 May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">June 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon 01 Jun 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Civil justice statistics quarterly: January to March 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 04 Jun 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thu 07 May 2026</t>
   </si>
   <si>
@@ -367,6 +355,9 @@
     <t xml:space="preserve">Thu 27 Aug 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Legal aid statistics quarterly: April to June 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mon 28 Sep 2026</t>
   </si>
   <si>
@@ -721,7 +712,7 @@
     <t xml:space="preserve">Coroners statistics</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 14 May 2026 (provisional)</t>
+    <t xml:space="preserve">Thu 14 May 2026 (confirmed)</t>
   </si>
   <si>
     <t xml:space="preserve">Criminal court statistics quarterly</t>
@@ -772,9 +763,6 @@
     <t xml:space="preserve">Electronic Monitoring Statistics Publication</t>
   </si>
   <si>
-    <t xml:space="preserve">Thu 23 Apr 2026 (confirmed)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ethnicity and the Criminal Justice System</t>
   </si>
   <si>
@@ -877,9 +865,6 @@
     <t xml:space="preserve">Prison Education and Accredited Programme Statistics</t>
   </si>
   <si>
-    <t xml:space="preserve">prison leavers in substance misuse treatment</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prison Performance Ratings</t>
   </si>
   <si>
@@ -923,9 +908,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unpaid work management information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu 14 May 2026 (confirmed)</t>
   </si>
   <si>
     <t xml:space="preserve">Thu 05 Nov 2026 (confirmed)</t>
@@ -1823,7 +1805,7 @@
         <v>17</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>18</v>
@@ -1850,29 +1832,31 @@
         <v>17</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="I9" s="7"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>17</v>
@@ -1881,25 +1865,25 @@
         <v>18</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I10" s="7"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>17</v>
@@ -1908,25 +1892,25 @@
         <v>18</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I11" s="7"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>17</v>
@@ -1935,25 +1919,25 @@
         <v>18</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I12" s="7"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>17</v>
@@ -1962,161 +1946,161 @@
         <v>18</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I13" s="7"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
       <c r="I14" s="7"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>24</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
       <c r="I15" s="7"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="F16" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="F17" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="H17" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="F19" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>20</v>
@@ -2124,26 +2108,24 @@
       <c r="G20" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="7"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="C21" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>20</v>
@@ -2152,115 +2134,105 @@
         <v>18</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
       <c r="F22" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="7"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>47</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
       <c r="I23" s="7"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="E24" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="F24" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I24" s="7"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I25" s="7"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>53</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
       <c r="F26" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>54</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
       <c r="I26" s="7"/>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -2274,52 +2246,64 @@
         <v>57</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
       <c r="F28" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I28" s="7"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>60</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>25</v>
@@ -2328,164 +2312,164 @@
         <v>18</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>62</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
       <c r="F30" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>54</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
       <c r="I30" s="7"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F31" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
       <c r="I31" s="7"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="F32" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
+        <v>27</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="I32" s="7"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+      <c r="F33" s="6" t="n">
+        <v>28</v>
+      </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="7"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>57</v>
-      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
       <c r="F34" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
       <c r="I34" s="7"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="D35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="F35" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="I35" s="7"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
       <c r="F36" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I36" s="7"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>30</v>
@@ -2494,25 +2478,25 @@
         <v>18</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>30</v>
@@ -2521,25 +2505,25 @@
         <v>18</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>30</v>
@@ -2548,25 +2532,25 @@
         <v>18</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I39" s="7"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>30</v>
@@ -2575,25 +2559,25 @@
         <v>18</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="I40" s="7"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>30</v>
@@ -2602,25 +2586,25 @@
         <v>18</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>30</v>
@@ -2629,25 +2613,25 @@
         <v>18</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>30</v>
@@ -2656,25 +2640,25 @@
         <v>18</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>30</v>
@@ -2683,25 +2667,25 @@
         <v>18</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>30</v>
@@ -2710,90 +2694,90 @@
         <v>18</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>25</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
       <c r="I46" s="7"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>81</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
       <c r="F47" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
       <c r="I47" s="7"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
+      <c r="D48" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I48" s="7"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
+        <v>94</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="F49" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I49" s="7"/>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2801,121 +2785,107 @@
         <v>94</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>97</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I50" s="7"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>101</v>
-      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
       <c r="F51" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>25</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
       <c r="I51" s="7"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>100</v>
-      </c>
       <c r="D52" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I52" s="7"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
-      <c r="F53" s="6" t="n">
-        <v>34</v>
-      </c>
+      <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="7"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I54" s="7"/>
     </row>
@@ -2927,7 +2897,9 @@
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
+      <c r="F55" s="6" t="n">
+        <v>37</v>
+      </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="7"/>
@@ -2943,114 +2915,114 @@
         <v>111</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I56" s="7"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
       <c r="F57" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I57" s="7"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D58" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F58" s="6" t="n">
         <v>39</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>38</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I58" s="7"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B59" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
       <c r="I59" s="7"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
+      <c r="F60" s="6" t="n">
+        <v>40</v>
+      </c>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
       <c r="I60" s="7"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -3058,17 +3030,29 @@
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
+      <c r="D62" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="F62" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I62" s="7"/>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -3082,25 +3066,25 @@
         <v>126</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I63" s="7"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>128</v>
@@ -3109,7 +3093,7 @@
         <v>129</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>130</v>
@@ -3121,25 +3105,25 @@
         <v>18</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="I64" s="7"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>43</v>
@@ -3148,25 +3132,25 @@
         <v>18</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="I65" s="7"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>43</v>
@@ -3175,25 +3159,25 @@
         <v>18</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I66" s="7"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>43</v>
@@ -3202,25 +3186,25 @@
         <v>18</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I67" s="7"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>43</v>
@@ -3229,119 +3213,119 @@
         <v>18</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
       <c r="I69" s="7"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
+      <c r="D70" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="I70" s="7"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I71" s="7"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I72" s="7"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B73" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="C73" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>46</v>
@@ -3350,52 +3334,52 @@
         <v>18</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B74" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>150</v>
-      </c>
       <c r="D74" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>153</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>47</v>
@@ -3404,28 +3388,28 @@
         <v>18</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I75" s="7"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>156</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>18</v>
@@ -3437,19 +3421,19 @@
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="C77" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="D77" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>48</v>
@@ -3458,48 +3442,48 @@
         <v>18</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="I77" s="7"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>54</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
       <c r="I78" s="7"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
+      <c r="D79" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I79" s="7"/>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3513,37 +3497,37 @@
         <v>166</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I80" s="7"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>50</v>
@@ -3552,7 +3536,7 @@
         <v>18</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I81" s="7"/>
     </row>
@@ -3560,39 +3544,27 @@
       <c r="A82" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B82" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>150</v>
-      </c>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
       <c r="F82" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>54</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
       <c r="I82" s="7"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
@@ -3600,42 +3572,42 @@
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
-      <c r="F84" s="6" t="n">
-        <v>52</v>
-      </c>
+      <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="6"/>
       <c r="I84" s="7"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
+      <c r="F85" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
       <c r="I85" s="7"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
@@ -3643,14 +3615,14 @@
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
@@ -3658,34 +3630,46 @@
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
+      <c r="D88" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>176</v>
+      </c>
       <c r="F88" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="I88" s="7"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>177</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>4</v>
@@ -3694,25 +3678,25 @@
         <v>18</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I89" s="7"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>4</v>
@@ -3721,25 +3705,25 @@
         <v>18</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I90" s="7"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B91" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E91" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>4</v>
@@ -3748,25 +3732,25 @@
         <v>18</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I91" s="7"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>182</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>4</v>
@@ -3781,19 +3765,19 @@
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E93" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>4</v>
@@ -3802,184 +3786,172 @@
         <v>18</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I93" s="7"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
       <c r="I94" s="7"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
+      <c r="F95" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
       <c r="I95" s="7"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
+      <c r="D96" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="F96" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I96" s="7"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I97" s="7"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B98" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>196</v>
-      </c>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
       <c r="F98" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>47</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
       <c r="I98" s="7"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
-      <c r="F99" s="6" t="n">
-        <v>8</v>
-      </c>
+      <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
       <c r="I99" s="7"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
+      <c r="D100" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I100" s="7"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B101" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>202</v>
-      </c>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
       <c r="F101" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>54</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
       <c r="I101" s="7"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
@@ -3987,17 +3959,29 @@
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E103" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
       <c r="F103" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I103" s="7"/>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -4005,78 +3989,51 @@
         <v>205</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I104" s="7"/>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I105" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:G6"/>
-  <conditionalFormatting sqref="A7:H106">
+  <conditionalFormatting sqref="A7:H105">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>=AND($A7&lt;&gt;$A6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I105">
+  <conditionalFormatting sqref="A7:I104">
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>=LEFT($A7, 3)="MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:H105">
+  <conditionalFormatting sqref="A7:H104">
     <cfRule type="expression" dxfId="2" priority="7">
       <formula>=LEFT($A7,3)&lt;&gt;"MON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B105">
+  <conditionalFormatting sqref="B7:B104">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>=AND($B7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A105">
+  <conditionalFormatting sqref="A7:A104">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=0,$E7=$E6)</formula>
     </cfRule>
@@ -4084,7 +4041,7 @@
       <formula>=AND(LEN($E7)&gt;0,MOD(RIGHT($E7,2),2)=1,$E7=$E6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D105">
+  <conditionalFormatting sqref="D7:D104">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>=AND($D7="confirmed")</formula>
     </cfRule>
@@ -4126,12 +4083,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -4146,46 +4103,46 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>222</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>225</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
@@ -4193,46 +4150,46 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H7" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="I7" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="K7" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" s="12" t="s">
+      <c r="L7" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="N7" s="12" t="s">
         <v>228</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>231</v>
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
@@ -4240,46 +4197,46 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
@@ -4287,46 +4244,46 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
@@ -4334,46 +4291,46 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="K10" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="L10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="N10" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>240</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
@@ -4381,46 +4338,46 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="J11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="L11" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>245</v>
-      </c>
       <c r="M11" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
@@ -4428,46 +4385,46 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
@@ -4475,46 +4432,46 @@
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
@@ -4522,46 +4479,46 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O14" s="13"/>
       <c r="P14" s="13"/>
@@ -4569,46 +4526,46 @@
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O15" s="13"/>
       <c r="P15" s="13"/>
@@ -4616,46 +4573,46 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
@@ -4663,46 +4620,46 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="O17" s="13"/>
       <c r="P17" s="13"/>
@@ -4710,44 +4667,44 @@
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
@@ -4755,46 +4712,46 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
@@ -4802,46 +4759,46 @@
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
@@ -4849,46 +4806,46 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
@@ -4896,46 +4853,46 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
@@ -4943,46 +4900,46 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
@@ -4990,46 +4947,46 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
@@ -5037,46 +4994,46 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
@@ -5084,46 +5041,46 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
@@ -5131,46 +5088,46 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
@@ -5178,46 +5135,46 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O28" s="13"/>
       <c r="P28" s="13"/>
@@ -5225,46 +5182,46 @@
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
@@ -5272,46 +5229,46 @@
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O30" s="13"/>
       <c r="P30" s="13"/>
@@ -5319,46 +5276,46 @@
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C31" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="L31" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>245</v>
-      </c>
       <c r="M31" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
@@ -5366,46 +5323,46 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
@@ -5413,44 +5370,46 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="B33" s="11"/>
+        <v>283</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="C33" s="12" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>227</v>
+        <v>267</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
@@ -5458,46 +5417,46 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>227</v>
+        <v>285</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O34" s="13"/>
       <c r="P34" s="13"/>
@@ -5505,46 +5464,46 @@
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>227</v>
+        <v>281</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>290</v>
+        <v>224</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O35" s="13"/>
       <c r="P35" s="13"/>
@@ -5552,46 +5511,46 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>285</v>
+        <v>224</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O36" s="13"/>
       <c r="P36" s="13"/>
@@ -5599,46 +5558,46 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>227</v>
+        <v>290</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
@@ -5646,46 +5605,46 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="L38" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>295</v>
-      </c>
       <c r="M38" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
@@ -5693,46 +5652,46 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>285</v>
+        <v>224</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
@@ -5740,46 +5699,46 @@
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>227</v>
+        <v>294</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O40" s="13"/>
       <c r="P40" s="13"/>
@@ -5787,46 +5746,46 @@
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="J41" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>227</v>
-      </c>
       <c r="K41" s="12" t="s">
-        <v>301</v>
+        <v>224</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O41" s="13"/>
       <c r="P41" s="13"/>
@@ -5834,46 +5793,46 @@
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>37</v>
+        <v>250</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>303</v>
+        <v>224</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>304</v>
+        <v>224</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
@@ -5881,101 +5840,54 @@
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O43" s="13"/>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="M44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="N44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="O44" s="13"/>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="13"/>
-    </row>
   </sheetData>
   <autoFilter ref="A6:N6"/>
-  <conditionalFormatting sqref="C7:N44">
+  <conditionalFormatting sqref="C7:N43">
     <cfRule type="expression" dxfId="5" priority="3">
       <formula>ISNUMBER(SEARCH("confirmed", INDIRECT("RC", FALSE)))</formula>
     </cfRule>
@@ -6011,12 +5923,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -6029,319 +5941,319 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B7" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/civil-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C7" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B8" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/community-performance-annual-update-to-march-2025", "Link to publication")</f>
       </c>
       <c r="C8" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B9" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/coroners-and-burials-statistics", "Link to publication")</f>
       </c>
       <c r="C9" s="11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B10" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-court-statistics", "Link to publication")</f>
       </c>
       <c r="C10" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B11" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C11" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B12" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/death-of-offenders-in-the-community", "Link to publication")</f>
       </c>
       <c r="C12" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B13" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/diversity-of-the-judiciary-2024-statistics", "Link to publication")</f>
       </c>
       <c r="C13" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B14" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/electronic-monitoring-statistics-annual-publication-march-2024", "Link to publication")</f>
       </c>
       <c r="C14" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B15" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/electronic-monitoring-publication", "Link to publication")</f>
       </c>
       <c r="C15" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B16" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/statistics/ethnicity-and-the-criminal-justice-system-2024", "Link to publication")</f>
       </c>
       <c r="C16" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G16" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>325</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B17" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/family-court-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C17" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B18" s="17" t="str">
         <f>HYPERLINK("NA", "Link to publication")</f>
@@ -6355,650 +6267,636 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B19" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/criminal-justice-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C19" s="11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B20" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C20" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B21" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-offender-equalities-report", "Link to publication")</f>
       </c>
       <c r="C21" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
       </c>
       <c r="C22" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/hmpps-annual-staff-equalities-report", "Link to publication")</f>
       </c>
       <c r="C23" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/justice-data-lab", "Link to publication")</f>
       </c>
       <c r="C24" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B25" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/knife-and-offensive-weapon-sentencing-statistics", "Link to publication")</f>
       </c>
       <c r="C25" s="11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B26" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/legal-aid-statistics", "Link to publication")</f>
       </c>
       <c r="C26" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B27" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/mortgage-and-landlord-possession-statistics", "Link to publication")</f>
       </c>
       <c r="C27" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B28" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/multi-agency-public-protection-arrangements-mappa-annual-reports", "Link to publication")</f>
       </c>
       <c r="C28" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B29" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-accommodation-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C29" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B30" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-employment-outcome-statistics", "Link to publication")</f>
       </c>
       <c r="C30" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B31" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/offender-management-statistics-quarterly", "Link to publication")</f>
       </c>
       <c r="C31" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B32" s="17" t="str">
         <f>HYPERLINK("https://www.gov.uk/government/collections/prison-education-statistics", "Link to publication")</f>
       </c>
       <c r="C32" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B33" s="17" t="str">
-        <f>HYPERLINK("NA", "Link to publication")</f>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B34" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-and-probation-trusts-performance-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
       </c>
       <c r="C34" s="11" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B35" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/prison-population-projections", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C35" s="11" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>376</v>
+        <v>327</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B36" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
       </c>
       <c r="C36" s="11" t="s">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>378</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B37" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/restricted-patients-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
       </c>
       <c r="C37" s="11" t="s">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
+        <v>375</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>377</v>
+      </c>
       <c r="G37" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B38" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/safety-in-custody-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
       </c>
       <c r="C38" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>319</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B39" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-custody-data", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
       </c>
       <c r="C39" s="11" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>384</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="11" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B40" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/proven-reoffending-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
       </c>
       <c r="C40" s="11" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
+        <v>382</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>312</v>
+      </c>
       <c r="G40" s="11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>387</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B41" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/tribunals-statistics", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
       </c>
       <c r="C41" s="11" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>319</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B42" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/unpaid-work-management-information", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
       </c>
       <c r="C42" s="11" t="s">
-        <v>37</v>
+        <v>250</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>322</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="G42" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="H42" s="11" t="s">
         <v>325</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B43" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/women-and-the-criminal-justice-system", "Link to publication")</f>
+        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
       </c>
       <c r="C43" s="11" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>330</v>
+        <v>384</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>330</v>
+        <v>386</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="B44" s="17" t="str">
-        <f>HYPERLINK("https://www.gov.uk/government/collections/youth-justice-statistics", "Link to publication")</f>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/Forward Look/Forward Look.xlsx
+++ b/Forward Look/Forward Look.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Click here to view on the gov.uk Research and Statistics calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Last updated:  Monday 27 April 2026</t>
+    <t xml:space="preserve">Last updated:  Wednesday 29 April 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Week Commencing</t>
